--- a/muban_clean/mudiban.xlsx
+++ b/muban_clean/mudiban.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="2019报价" sheetId="15" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'2019报价'!$A$1:$I$168</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1403,6 +1406,13 @@
     <font>
       <vertAlign val="superscript"/>
       <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="新宋体"/>
       <charset val="134"/>
@@ -1410,14 +1420,7 @@
     <font>
       <vertAlign val="superscript"/>
       <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <vertAlign val="superscript"/>
-      <sz val="11"/>
-      <name val="宋体"/>
+      <name val="新宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1430,7 +1433,7 @@
     <font>
       <vertAlign val="superscript"/>
       <sz val="11"/>
-      <name val="新宋体"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1443,13 +1446,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="22"/>
+        <fgColor indexed="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="9"/>
+        <fgColor theme="0" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1782,10 +1785,10 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
+      <left style="thin">
         <color auto="1"/>
-      </right>
+      </left>
+      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -1795,10 +1798,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right style="thin">
         <color auto="1"/>
-      </left>
-      <right/>
+      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -2098,7 +2101,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2114,13 +2117,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2129,18 +2132,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2235,233 +2238,254 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="14" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="13" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="14" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="177" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="14" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="13" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="14" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2470,31 +2494,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="12" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="66">
@@ -2885,7 +2915,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:FM168"/>
+  <dimension ref="A1:FO168"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4.08333333333333" style="19" customWidth="1"/>
@@ -3607,10 +3637,36 @@
         <v>22</v>
       </c>
       <c r="J11" s="51"/>
-      <c r="K11" s="52"/>
-      <c r="L11" s="52" t="s">
+      <c r="K11" s="51"/>
+      <c r="L11" s="51" t="s">
         <v>23</v>
       </c>
+      <c r="M11" s="52"/>
+      <c r="N11" s="52"/>
+      <c r="O11" s="52"/>
+      <c r="P11" s="52"/>
+      <c r="Q11" s="52"/>
+      <c r="R11" s="52"/>
+      <c r="S11" s="52"/>
+      <c r="T11" s="52"/>
+      <c r="U11" s="52"/>
+      <c r="V11" s="52"/>
+      <c r="W11" s="52"/>
+      <c r="X11" s="52"/>
+      <c r="Y11" s="52"/>
+      <c r="Z11" s="52"/>
+      <c r="AA11" s="52"/>
+      <c r="AB11" s="52"/>
+      <c r="AC11" s="52"/>
+      <c r="AD11" s="52"/>
+      <c r="AE11" s="52"/>
+      <c r="AF11" s="52"/>
+      <c r="AG11" s="52"/>
+      <c r="AH11" s="52"/>
+      <c r="AI11" s="52"/>
+      <c r="AJ11" s="52"/>
+      <c r="AK11" s="52"/>
+      <c r="AL11" s="53"/>
     </row>
     <row r="12" ht="16.5" customHeight="1" spans="1:169">
       <c r="A12" s="42">
@@ -3637,18 +3693,43 @@
         <f>C12*G12</f>
         <v>0</v>
       </c>
-      <c r="I12" s="41" t="s">
+      <c r="I12" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="33"/>
+      <c r="J12" s="55"/>
+      <c r="K12" s="55"/>
+      <c r="L12" s="55"/>
+      <c r="M12" s="56"/>
+      <c r="N12" s="56"/>
+      <c r="O12" s="56"/>
+      <c r="P12" s="56"/>
+      <c r="Q12" s="56"/>
+      <c r="R12" s="56"/>
+      <c r="S12" s="56"/>
+      <c r="T12" s="56"/>
+      <c r="U12" s="56"/>
+      <c r="V12" s="56"/>
+      <c r="W12" s="56"/>
+      <c r="X12" s="56"/>
+      <c r="Y12" s="56"/>
+      <c r="Z12" s="56"/>
+      <c r="AA12" s="56"/>
+      <c r="AB12" s="56"/>
+      <c r="AC12" s="56"/>
+      <c r="AD12" s="56"/>
+      <c r="AE12" s="56"/>
+      <c r="AF12" s="56"/>
+      <c r="AG12" s="56"/>
+      <c r="AH12" s="56"/>
+      <c r="AI12" s="56"/>
+      <c r="AJ12" s="56"/>
+      <c r="AK12" s="56"/>
     </row>
     <row r="13" s="5" customFormat="1" ht="17.25" customHeight="1" spans="1:169">
       <c r="A13" s="42">
         <v>5</v>
       </c>
-      <c r="B13" s="53" t="s">
+      <c r="B13" s="57" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="40"/>
@@ -3669,16 +3750,44 @@
         <f>C13*G13</f>
         <v>0</v>
       </c>
-      <c r="I13" s="54" t="s">
+      <c r="I13" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="J13" s="55"/>
+      <c r="J13" s="59"/>
+      <c r="K13" s="59"/>
+      <c r="L13" s="59"/>
+      <c r="M13" s="59"/>
+      <c r="N13" s="59"/>
+      <c r="O13" s="59"/>
+      <c r="P13" s="59"/>
+      <c r="Q13" s="59"/>
+      <c r="R13" s="59"/>
+      <c r="S13" s="59"/>
+      <c r="T13" s="59"/>
+      <c r="U13" s="59"/>
+      <c r="V13" s="59"/>
+      <c r="W13" s="59"/>
+      <c r="X13" s="59"/>
+      <c r="Y13" s="59"/>
+      <c r="Z13" s="59"/>
+      <c r="AA13" s="59"/>
+      <c r="AB13" s="59"/>
+      <c r="AC13" s="59"/>
+      <c r="AD13" s="59"/>
+      <c r="AE13" s="59"/>
+      <c r="AF13" s="59"/>
+      <c r="AG13" s="59"/>
+      <c r="AH13" s="59"/>
+      <c r="AI13" s="59"/>
+      <c r="AJ13" s="59"/>
+      <c r="AK13" s="59"/>
+      <c r="AL13" s="60"/>
     </row>
     <row r="14" s="5" customFormat="1" ht="17.25" customHeight="1" spans="1:169">
       <c r="A14" s="42">
         <v>6</v>
       </c>
-      <c r="B14" s="56" t="s">
+      <c r="B14" s="61" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="40"/>
@@ -3699,16 +3808,44 @@
         <f>C14*G14</f>
         <v>0</v>
       </c>
-      <c r="I14" s="54" t="s">
+      <c r="I14" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="J14" s="55"/>
+      <c r="J14" s="59"/>
+      <c r="K14" s="59"/>
+      <c r="L14" s="59"/>
+      <c r="M14" s="59"/>
+      <c r="N14" s="59"/>
+      <c r="O14" s="59"/>
+      <c r="P14" s="59"/>
+      <c r="Q14" s="59"/>
+      <c r="R14" s="59"/>
+      <c r="S14" s="59"/>
+      <c r="T14" s="59"/>
+      <c r="U14" s="59"/>
+      <c r="V14" s="59"/>
+      <c r="W14" s="59"/>
+      <c r="X14" s="59"/>
+      <c r="Y14" s="59"/>
+      <c r="Z14" s="59"/>
+      <c r="AA14" s="59"/>
+      <c r="AB14" s="59"/>
+      <c r="AC14" s="59"/>
+      <c r="AD14" s="59"/>
+      <c r="AE14" s="59"/>
+      <c r="AF14" s="59"/>
+      <c r="AG14" s="59"/>
+      <c r="AH14" s="59"/>
+      <c r="AI14" s="59"/>
+      <c r="AJ14" s="59"/>
+      <c r="AK14" s="59"/>
+      <c r="AL14" s="60"/>
     </row>
     <row r="15" ht="17.25" customHeight="1" spans="1:169">
       <c r="A15" s="42">
         <v>7</v>
       </c>
-      <c r="B15" s="54" t="s">
+      <c r="B15" s="62" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="40"/>
@@ -3729,7 +3866,7 @@
         <f>C15*G15</f>
         <v>0</v>
       </c>
-      <c r="I15" s="54" t="s">
+      <c r="I15" s="62" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3737,7 +3874,7 @@
       <c r="A16" s="42">
         <v>8</v>
       </c>
-      <c r="B16" s="57" t="s">
+      <c r="B16" s="63" t="s">
         <v>32</v>
       </c>
       <c r="C16" s="49"/>
@@ -3758,12 +3895,12 @@
         <f>C16*G16</f>
         <v>0</v>
       </c>
-      <c r="I16" s="50" t="s">
+      <c r="I16" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="58"/>
-      <c r="K16" s="58"/>
-      <c r="L16" s="58"/>
+      <c r="J16" s="65"/>
+      <c r="K16" s="65"/>
+      <c r="L16" s="65"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" spans="1:12">
       <c r="A17" s="42">
@@ -3801,7 +3938,7 @@
       <c r="A18" s="42">
         <v>10</v>
       </c>
-      <c r="B18" s="59" t="s">
+      <c r="B18" s="66" t="s">
         <v>36</v>
       </c>
       <c r="C18" s="42"/>
@@ -3822,7 +3959,7 @@
         <f>SUM(G18*C18)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="54" t="s">
+      <c r="I18" s="62" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4019,32 +4156,32 @@
       <c r="L24" s="33"/>
     </row>
     <row r="25" s="7" customFormat="1" ht="18" customHeight="1" spans="1:12">
-      <c r="A25" s="60"/>
-      <c r="B25" s="61" t="s">
+      <c r="A25" s="67"/>
+      <c r="B25" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="60"/>
-      <c r="D25" s="60"/>
-      <c r="E25" s="60"/>
-      <c r="F25" s="60">
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="67"/>
+      <c r="F25" s="67">
         <f>SUM(F9:F24)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="60"/>
-      <c r="H25" s="60">
+      <c r="G25" s="67"/>
+      <c r="H25" s="67">
         <f>SUM(H9:H24)</f>
         <v>0</v>
       </c>
-      <c r="I25" s="62"/>
-      <c r="J25" s="63"/>
-      <c r="K25" s="63"/>
-      <c r="L25" s="63"/>
+      <c r="I25" s="69"/>
+      <c r="J25" s="70"/>
+      <c r="K25" s="70"/>
+      <c r="L25" s="70"/>
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:12">
       <c r="A26" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="64" t="s">
+      <c r="B26" s="71" t="s">
         <v>54</v>
       </c>
       <c r="C26" s="40"/>
@@ -4062,7 +4199,7 @@
       <c r="A27" s="49">
         <v>1</v>
       </c>
-      <c r="B27" s="65" t="s">
+      <c r="B27" s="72" t="s">
         <v>55</v>
       </c>
       <c r="C27" s="49"/>
@@ -4083,18 +4220,18 @@
         <f t="shared" ref="H27:H32" si="4">SUM(G27*C27)</f>
         <v>0</v>
       </c>
-      <c r="I27" s="50" t="s">
+      <c r="I27" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="J27" s="58"/>
-      <c r="K27" s="58"/>
-      <c r="L27" s="58"/>
+      <c r="J27" s="65"/>
+      <c r="K27" s="65"/>
+      <c r="L27" s="65"/>
     </row>
     <row r="28" s="6" customFormat="1" ht="15" customHeight="1" spans="1:12">
       <c r="A28" s="49">
         <v>2</v>
       </c>
-      <c r="B28" s="65" t="s">
+      <c r="B28" s="72" t="s">
         <v>56</v>
       </c>
       <c r="C28" s="49"/>
@@ -4115,12 +4252,12 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I28" s="50" t="s">
+      <c r="I28" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="J28" s="58"/>
-      <c r="K28" s="58"/>
-      <c r="L28" s="58"/>
+      <c r="J28" s="65"/>
+      <c r="K28" s="65"/>
+      <c r="L28" s="65"/>
     </row>
     <row r="29" ht="16" customHeight="1" spans="1:12">
       <c r="A29" s="49">
@@ -4158,7 +4295,7 @@
       <c r="A30" s="49">
         <v>4</v>
       </c>
-      <c r="B30" s="66" t="s">
+      <c r="B30" s="73" t="s">
         <v>60</v>
       </c>
       <c r="C30" s="40"/>
@@ -4182,9 +4319,9 @@
       <c r="I30" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="J30" s="67"/>
-      <c r="K30" s="67"/>
-      <c r="L30" s="67"/>
+      <c r="J30" s="74"/>
+      <c r="K30" s="74"/>
+      <c r="L30" s="74"/>
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:12">
       <c r="A31" s="49">
@@ -4283,32 +4420,32 @@
       <c r="L33" s="33"/>
     </row>
     <row r="34" s="9" customFormat="1" ht="17.25" customHeight="1" spans="1:12">
-      <c r="A34" s="68"/>
-      <c r="B34" s="69" t="s">
+      <c r="A34" s="75"/>
+      <c r="B34" s="76" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="68"/>
-      <c r="D34" s="68"/>
-      <c r="E34" s="70"/>
-      <c r="F34" s="71">
+      <c r="C34" s="75"/>
+      <c r="D34" s="75"/>
+      <c r="E34" s="77"/>
+      <c r="F34" s="78">
         <f>SUM(F27:F33)</f>
         <v>0</v>
       </c>
-      <c r="G34" s="68"/>
-      <c r="H34" s="71">
+      <c r="G34" s="75"/>
+      <c r="H34" s="78">
         <f>SUM(H27:H33)</f>
         <v>0</v>
       </c>
-      <c r="I34" s="72"/>
-      <c r="J34" s="73"/>
-      <c r="K34" s="73"/>
-      <c r="L34" s="73"/>
+      <c r="I34" s="79"/>
+      <c r="J34" s="80"/>
+      <c r="K34" s="80"/>
+      <c r="L34" s="80"/>
     </row>
     <row r="35" ht="17.25" customHeight="1" spans="1:12">
       <c r="A35" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="B35" s="64" t="s">
+      <c r="B35" s="71" t="s">
         <v>66</v>
       </c>
       <c r="C35" s="40"/>
@@ -4326,7 +4463,7 @@
       <c r="A36" s="49">
         <v>1</v>
       </c>
-      <c r="B36" s="65" t="s">
+      <c r="B36" s="72" t="s">
         <v>55</v>
       </c>
       <c r="C36" s="49"/>
@@ -4347,18 +4484,18 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I36" s="50" t="s">
+      <c r="I36" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="J36" s="58"/>
-      <c r="K36" s="58"/>
-      <c r="L36" s="58"/>
+      <c r="J36" s="65"/>
+      <c r="K36" s="65"/>
+      <c r="L36" s="65"/>
     </row>
     <row r="37" s="6" customFormat="1" ht="14.25" customHeight="1" spans="1:12">
       <c r="A37" s="49">
         <v>2</v>
       </c>
-      <c r="B37" s="65" t="s">
+      <c r="B37" s="72" t="s">
         <v>56</v>
       </c>
       <c r="C37" s="49"/>
@@ -4379,12 +4516,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I37" s="50" t="s">
+      <c r="I37" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="J37" s="58"/>
-      <c r="K37" s="58"/>
-      <c r="L37" s="58"/>
+      <c r="J37" s="65"/>
+      <c r="K37" s="65"/>
+      <c r="L37" s="65"/>
     </row>
     <row r="38" ht="16" customHeight="1" spans="1:12">
       <c r="A38" s="49">
@@ -4422,7 +4559,7 @@
       <c r="A39" s="49">
         <v>4</v>
       </c>
-      <c r="B39" s="66" t="s">
+      <c r="B39" s="73" t="s">
         <v>60</v>
       </c>
       <c r="C39" s="40"/>
@@ -4446,9 +4583,9 @@
       <c r="I39" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="J39" s="67"/>
-      <c r="K39" s="67"/>
-      <c r="L39" s="67"/>
+      <c r="J39" s="74"/>
+      <c r="K39" s="74"/>
+      <c r="L39" s="74"/>
     </row>
     <row r="40" ht="14" customHeight="1" spans="1:12">
       <c r="A40" s="49">
@@ -4609,37 +4746,37 @@
       <c r="L44" s="33"/>
     </row>
     <row r="45" s="7" customFormat="1" ht="18" customHeight="1" spans="1:12">
-      <c r="A45" s="60"/>
-      <c r="B45" s="61" t="s">
+      <c r="A45" s="67"/>
+      <c r="B45" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="C45" s="60"/>
-      <c r="D45" s="60"/>
-      <c r="E45" s="60"/>
-      <c r="F45" s="60">
+      <c r="C45" s="67"/>
+      <c r="D45" s="67"/>
+      <c r="E45" s="67"/>
+      <c r="F45" s="67">
         <f>SUM(F36:F44)</f>
         <v>0</v>
       </c>
-      <c r="G45" s="60"/>
-      <c r="H45" s="60">
+      <c r="G45" s="67"/>
+      <c r="H45" s="67">
         <f>SUM(H36:H44)</f>
         <v>0</v>
       </c>
-      <c r="I45" s="62"/>
-      <c r="J45" s="63"/>
-      <c r="K45" s="63"/>
-      <c r="L45" s="63"/>
+      <c r="I45" s="69"/>
+      <c r="J45" s="70"/>
+      <c r="K45" s="70"/>
+      <c r="L45" s="70"/>
     </row>
     <row r="46" ht="18.75" customHeight="1" spans="1:12">
       <c r="A46" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="B46" s="74" t="s">
+      <c r="B46" s="81" t="s">
         <v>73</v>
       </c>
-      <c r="C46" s="75"/>
-      <c r="D46" s="75"/>
-      <c r="E46" s="76"/>
+      <c r="C46" s="82"/>
+      <c r="D46" s="82"/>
+      <c r="E46" s="83"/>
       <c r="F46" s="40"/>
       <c r="G46" s="40"/>
       <c r="H46" s="40"/>
@@ -4652,7 +4789,7 @@
       <c r="A47" s="49">
         <v>1</v>
       </c>
-      <c r="B47" s="65" t="s">
+      <c r="B47" s="72" t="s">
         <v>74</v>
       </c>
       <c r="C47" s="49"/>
@@ -4673,12 +4810,12 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I47" s="50" t="s">
+      <c r="I47" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="J47" s="77"/>
-      <c r="K47" s="77"/>
-      <c r="L47" s="77"/>
+      <c r="J47" s="84"/>
+      <c r="K47" s="84"/>
+      <c r="L47" s="84"/>
     </row>
     <row r="48" ht="17" customHeight="1" spans="1:12">
       <c r="A48" s="49">
@@ -4806,26 +4943,26 @@
       <c r="L51" s="33"/>
     </row>
     <row r="52" s="7" customFormat="1" ht="18" customHeight="1" spans="1:12">
-      <c r="A52" s="60"/>
-      <c r="B52" s="61" t="s">
+      <c r="A52" s="67"/>
+      <c r="B52" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="C52" s="60"/>
-      <c r="D52" s="60"/>
-      <c r="E52" s="60"/>
-      <c r="F52" s="60">
+      <c r="C52" s="67"/>
+      <c r="D52" s="67"/>
+      <c r="E52" s="67"/>
+      <c r="F52" s="67">
         <f>SUM(F47:F51)</f>
         <v>0</v>
       </c>
-      <c r="G52" s="60"/>
-      <c r="H52" s="60">
+      <c r="G52" s="67"/>
+      <c r="H52" s="67">
         <f>SUM(H47:H51)</f>
         <v>0</v>
       </c>
-      <c r="I52" s="62"/>
-      <c r="J52" s="63"/>
-      <c r="K52" s="63"/>
-      <c r="L52" s="63"/>
+      <c r="I52" s="69"/>
+      <c r="J52" s="70"/>
+      <c r="K52" s="70"/>
+      <c r="L52" s="70"/>
     </row>
     <row r="53" ht="18" customHeight="1" spans="1:12">
       <c r="A53" s="38" t="s">
@@ -4849,7 +4986,7 @@
       <c r="A54" s="49">
         <v>1</v>
       </c>
-      <c r="B54" s="65" t="s">
+      <c r="B54" s="72" t="s">
         <v>55</v>
       </c>
       <c r="C54" s="49"/>
@@ -4870,18 +5007,18 @@
         <f t="shared" ref="H54:H56" si="10">SUM(G54*C54)</f>
         <v>0</v>
       </c>
-      <c r="I54" s="50" t="s">
+      <c r="I54" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="J54" s="58"/>
-      <c r="K54" s="58"/>
-      <c r="L54" s="58"/>
+      <c r="J54" s="65"/>
+      <c r="K54" s="65"/>
+      <c r="L54" s="65"/>
     </row>
     <row r="55" s="6" customFormat="1" ht="15" customHeight="1" spans="1:12">
       <c r="A55" s="49">
         <v>2</v>
       </c>
-      <c r="B55" s="65" t="s">
+      <c r="B55" s="72" t="s">
         <v>56</v>
       </c>
       <c r="C55" s="49"/>
@@ -4902,12 +5039,12 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I55" s="50" t="s">
+      <c r="I55" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="J55" s="58"/>
-      <c r="K55" s="58"/>
-      <c r="L55" s="58"/>
+      <c r="J55" s="65"/>
+      <c r="K55" s="65"/>
+      <c r="L55" s="65"/>
     </row>
     <row r="56" ht="16" customHeight="1" spans="1:12">
       <c r="A56" s="49">
@@ -4945,7 +5082,7 @@
       <c r="A57" s="49">
         <v>4</v>
       </c>
-      <c r="B57" s="66" t="s">
+      <c r="B57" s="73" t="s">
         <v>60</v>
       </c>
       <c r="C57" s="40"/>
@@ -4969,9 +5106,9 @@
       <c r="I57" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="J57" s="67"/>
-      <c r="K57" s="67"/>
-      <c r="L57" s="67"/>
+      <c r="J57" s="74"/>
+      <c r="K57" s="74"/>
+      <c r="L57" s="74"/>
     </row>
     <row r="58" ht="15" customHeight="1" spans="1:12">
       <c r="A58" s="49">
@@ -5132,26 +5269,26 @@
       <c r="L62" s="33"/>
     </row>
     <row r="63" s="7" customFormat="1" ht="16.5" customHeight="1" spans="1:12">
-      <c r="A63" s="60"/>
-      <c r="B63" s="61" t="s">
+      <c r="A63" s="67"/>
+      <c r="B63" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="C63" s="60"/>
-      <c r="D63" s="60"/>
-      <c r="E63" s="60"/>
-      <c r="F63" s="60">
+      <c r="C63" s="67"/>
+      <c r="D63" s="67"/>
+      <c r="E63" s="67"/>
+      <c r="F63" s="67">
         <f>SUM(F54:F62)</f>
         <v>0</v>
       </c>
-      <c r="G63" s="60"/>
-      <c r="H63" s="60">
+      <c r="G63" s="67"/>
+      <c r="H63" s="67">
         <f>SUM(H54:H62)</f>
         <v>0</v>
       </c>
-      <c r="I63" s="62"/>
-      <c r="J63" s="63"/>
-      <c r="K63" s="63"/>
-      <c r="L63" s="63"/>
+      <c r="I63" s="69"/>
+      <c r="J63" s="70"/>
+      <c r="K63" s="70"/>
+      <c r="L63" s="70"/>
     </row>
     <row r="64" ht="18" customHeight="1" spans="1:12">
       <c r="A64" s="38" t="s">
@@ -5175,7 +5312,7 @@
       <c r="A65" s="49">
         <v>1</v>
       </c>
-      <c r="B65" s="65" t="s">
+      <c r="B65" s="72" t="s">
         <v>74</v>
       </c>
       <c r="C65" s="49"/>
@@ -5196,12 +5333,12 @@
         <f>SUM(G65*C65)</f>
         <v>0</v>
       </c>
-      <c r="I65" s="50" t="s">
+      <c r="I65" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="J65" s="77"/>
-      <c r="K65" s="77"/>
-      <c r="L65" s="77"/>
+      <c r="J65" s="84"/>
+      <c r="K65" s="84"/>
+      <c r="L65" s="84"/>
     </row>
     <row r="66" s="10" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
       <c r="A66" s="49">
@@ -5332,26 +5469,26 @@
       <c r="L69" s="33"/>
     </row>
     <row r="70" s="7" customFormat="1" ht="18" customHeight="1" spans="1:12">
-      <c r="A70" s="60"/>
-      <c r="B70" s="61" t="s">
+      <c r="A70" s="67"/>
+      <c r="B70" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="C70" s="60"/>
-      <c r="D70" s="60"/>
-      <c r="E70" s="60"/>
-      <c r="F70" s="60">
+      <c r="C70" s="67"/>
+      <c r="D70" s="67"/>
+      <c r="E70" s="67"/>
+      <c r="F70" s="67">
         <f>SUM(F65:F69)</f>
         <v>0</v>
       </c>
-      <c r="G70" s="60"/>
-      <c r="H70" s="60">
+      <c r="G70" s="67"/>
+      <c r="H70" s="67">
         <f>SUM(H65:H69)</f>
         <v>0</v>
       </c>
-      <c r="I70" s="62"/>
-      <c r="J70" s="63"/>
-      <c r="K70" s="63"/>
-      <c r="L70" s="63"/>
+      <c r="I70" s="69"/>
+      <c r="J70" s="70"/>
+      <c r="K70" s="70"/>
+      <c r="L70" s="70"/>
     </row>
     <row r="71" ht="18" customHeight="1" spans="1:12">
       <c r="A71" s="38" t="s">
@@ -5375,7 +5512,7 @@
       <c r="A72" s="49">
         <v>1</v>
       </c>
-      <c r="B72" s="65" t="s">
+      <c r="B72" s="72" t="s">
         <v>74</v>
       </c>
       <c r="C72" s="49"/>
@@ -5396,12 +5533,12 @@
         <f>SUM(G72*C72)</f>
         <v>0</v>
       </c>
-      <c r="I72" s="50" t="s">
+      <c r="I72" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="J72" s="77"/>
-      <c r="K72" s="77"/>
-      <c r="L72" s="77"/>
+      <c r="J72" s="84"/>
+      <c r="K72" s="84"/>
+      <c r="L72" s="84"/>
     </row>
     <row r="73" ht="16.5" customHeight="1" spans="1:12">
       <c r="A73" s="49">
@@ -5500,26 +5637,26 @@
       <c r="L75" s="33"/>
     </row>
     <row r="76" s="7" customFormat="1" ht="18" customHeight="1" spans="1:12">
-      <c r="A76" s="60"/>
-      <c r="B76" s="61" t="s">
+      <c r="A76" s="67"/>
+      <c r="B76" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="C76" s="60"/>
-      <c r="D76" s="60"/>
-      <c r="E76" s="60"/>
-      <c r="F76" s="60">
+      <c r="C76" s="67"/>
+      <c r="D76" s="67"/>
+      <c r="E76" s="67"/>
+      <c r="F76" s="67">
         <f>SUM(F72:F75)</f>
         <v>0</v>
       </c>
-      <c r="G76" s="60"/>
-      <c r="H76" s="60">
+      <c r="G76" s="67"/>
+      <c r="H76" s="67">
         <f>SUM(H72:H75)</f>
         <v>0</v>
       </c>
-      <c r="I76" s="62"/>
-      <c r="J76" s="63"/>
-      <c r="K76" s="63"/>
-      <c r="L76" s="63"/>
+      <c r="I76" s="69"/>
+      <c r="J76" s="70"/>
+      <c r="K76" s="70"/>
+      <c r="L76" s="70"/>
     </row>
     <row r="77" ht="16.5" customHeight="1" spans="1:12">
       <c r="A77" s="38" t="s">
@@ -5543,12 +5680,12 @@
       <c r="A78" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="B78" s="78" t="s">
+      <c r="B78" s="85" t="s">
         <v>88</v>
       </c>
-      <c r="C78" s="79"/>
-      <c r="D78" s="79"/>
-      <c r="E78" s="80"/>
+      <c r="C78" s="86"/>
+      <c r="D78" s="86"/>
+      <c r="E78" s="87"/>
       <c r="F78" s="40"/>
       <c r="G78" s="40"/>
       <c r="H78" s="40"/>
@@ -5561,7 +5698,7 @@
       <c r="A79" s="49">
         <v>1</v>
       </c>
-      <c r="B79" s="65" t="s">
+      <c r="B79" s="72" t="s">
         <v>89</v>
       </c>
       <c r="C79" s="49"/>
@@ -5576,18 +5713,18 @@
         <v>12</v>
       </c>
       <c r="H79" s="49"/>
-      <c r="I79" s="50" t="s">
+      <c r="I79" s="64" t="s">
         <v>90</v>
       </c>
-      <c r="J79" s="58"/>
-      <c r="K79" s="58"/>
-      <c r="L79" s="58"/>
+      <c r="J79" s="65"/>
+      <c r="K79" s="65"/>
+      <c r="L79" s="65"/>
     </row>
     <row r="80" s="6" customFormat="1" ht="15" customHeight="1" spans="1:12">
       <c r="A80" s="49">
         <v>2</v>
       </c>
-      <c r="B80" s="65" t="s">
+      <c r="B80" s="72" t="s">
         <v>91</v>
       </c>
       <c r="C80" s="49"/>
@@ -5602,18 +5739,18 @@
         <v>11</v>
       </c>
       <c r="H80" s="49"/>
-      <c r="I80" s="50" t="s">
+      <c r="I80" s="64" t="s">
         <v>92</v>
       </c>
-      <c r="J80" s="58"/>
-      <c r="K80" s="58"/>
-      <c r="L80" s="58"/>
+      <c r="J80" s="65"/>
+      <c r="K80" s="65"/>
+      <c r="L80" s="65"/>
     </row>
     <row r="81" s="6" customFormat="1" ht="15" customHeight="1" spans="1:12">
       <c r="A81" s="49">
         <v>3</v>
       </c>
-      <c r="B81" s="65" t="s">
+      <c r="B81" s="72" t="s">
         <v>93</v>
       </c>
       <c r="C81" s="49"/>
@@ -5628,18 +5765,18 @@
         <v>11</v>
       </c>
       <c r="H81" s="49"/>
-      <c r="I81" s="50" t="s">
+      <c r="I81" s="64" t="s">
         <v>94</v>
       </c>
-      <c r="J81" s="58"/>
-      <c r="K81" s="58"/>
-      <c r="L81" s="58"/>
+      <c r="J81" s="65"/>
+      <c r="K81" s="65"/>
+      <c r="L81" s="65"/>
     </row>
     <row r="82" s="6" customFormat="1" ht="15" customHeight="1" spans="1:12">
       <c r="A82" s="49">
         <v>4</v>
       </c>
-      <c r="B82" s="65" t="s">
+      <c r="B82" s="72" t="s">
         <v>95</v>
       </c>
       <c r="C82" s="49"/>
@@ -5654,18 +5791,18 @@
         <v>11</v>
       </c>
       <c r="H82" s="49"/>
-      <c r="I82" s="50" t="s">
+      <c r="I82" s="64" t="s">
         <v>94</v>
       </c>
-      <c r="J82" s="58"/>
-      <c r="K82" s="58"/>
-      <c r="L82" s="58"/>
+      <c r="J82" s="65"/>
+      <c r="K82" s="65"/>
+      <c r="L82" s="65"/>
     </row>
     <row r="83" s="6" customFormat="1" ht="15" customHeight="1" spans="1:12">
       <c r="A83" s="49">
         <v>5</v>
       </c>
-      <c r="B83" s="65" t="s">
+      <c r="B83" s="72" t="s">
         <v>96</v>
       </c>
       <c r="C83" s="49"/>
@@ -5680,12 +5817,12 @@
         <v>11</v>
       </c>
       <c r="H83" s="49"/>
-      <c r="I83" s="50" t="s">
+      <c r="I83" s="64" t="s">
         <v>94</v>
       </c>
-      <c r="J83" s="58"/>
-      <c r="K83" s="58"/>
-      <c r="L83" s="58"/>
+      <c r="J83" s="65"/>
+      <c r="K83" s="65"/>
+      <c r="L83" s="65"/>
     </row>
     <row r="84" ht="15" customHeight="1" spans="1:12">
       <c r="A84" s="40">
@@ -5769,7 +5906,7 @@
       <c r="A87" s="49">
         <v>9</v>
       </c>
-      <c r="B87" s="65" t="s">
+      <c r="B87" s="72" t="s">
         <v>104</v>
       </c>
       <c r="C87" s="49"/>
@@ -5784,18 +5921,18 @@
         <v>13</v>
       </c>
       <c r="H87" s="49"/>
-      <c r="I87" s="81" t="s">
+      <c r="I87" s="88" t="s">
         <v>105</v>
       </c>
-      <c r="J87" s="58"/>
-      <c r="K87" s="58"/>
-      <c r="L87" s="58"/>
+      <c r="J87" s="65"/>
+      <c r="K87" s="65"/>
+      <c r="L87" s="65"/>
     </row>
     <row r="88" s="6" customFormat="1" ht="22.5" customHeight="1" spans="1:12">
       <c r="A88" s="49">
         <v>10</v>
       </c>
-      <c r="B88" s="65" t="s">
+      <c r="B88" s="72" t="s">
         <v>106</v>
       </c>
       <c r="C88" s="49"/>
@@ -5809,19 +5946,19 @@
       <c r="G88" s="49">
         <v>15</v>
       </c>
-      <c r="H88" s="82"/>
-      <c r="I88" s="81" t="s">
+      <c r="H88" s="89"/>
+      <c r="I88" s="88" t="s">
         <v>107</v>
       </c>
-      <c r="J88" s="58"/>
-      <c r="K88" s="58"/>
-      <c r="L88" s="58"/>
+      <c r="J88" s="65"/>
+      <c r="K88" s="65"/>
+      <c r="L88" s="65"/>
     </row>
     <row r="89" s="6" customFormat="1" ht="22.5" customHeight="1" spans="1:12">
       <c r="A89" s="49">
         <v>11</v>
       </c>
-      <c r="B89" s="65" t="s">
+      <c r="B89" s="72" t="s">
         <v>108</v>
       </c>
       <c r="C89" s="49"/>
@@ -5835,13 +5972,13 @@
       <c r="G89" s="49">
         <v>20</v>
       </c>
-      <c r="H89" s="82"/>
-      <c r="I89" s="81" t="s">
+      <c r="H89" s="89"/>
+      <c r="I89" s="88" t="s">
         <v>109</v>
       </c>
-      <c r="J89" s="58"/>
-      <c r="K89" s="58"/>
-      <c r="L89" s="58"/>
+      <c r="J89" s="65"/>
+      <c r="K89" s="65"/>
+      <c r="L89" s="65"/>
     </row>
     <row r="90" ht="15.75" customHeight="1" spans="1:12">
       <c r="A90" s="40">
@@ -5925,52 +6062,52 @@
       <c r="A93" s="40">
         <v>15</v>
       </c>
-      <c r="B93" s="66" t="s">
+      <c r="B93" s="73" t="s">
         <v>115</v>
       </c>
-      <c r="C93" s="83"/>
+      <c r="C93" s="90"/>
       <c r="D93" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E93" s="83"/>
+      <c r="E93" s="90"/>
       <c r="F93" s="40"/>
       <c r="G93" s="40">
         <v>5</v>
       </c>
       <c r="H93" s="44"/>
-      <c r="I93" s="84" t="s">
+      <c r="I93" s="91" t="s">
         <v>116</v>
       </c>
       <c r="J93" s="33"/>
-      <c r="K93" s="85"/>
-      <c r="L93" s="85"/>
+      <c r="K93" s="92"/>
+      <c r="L93" s="92"/>
     </row>
     <row r="94" s="7" customFormat="1" ht="16.5" customHeight="1" spans="1:12">
-      <c r="A94" s="60"/>
-      <c r="B94" s="61" t="s">
+      <c r="A94" s="67"/>
+      <c r="B94" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="C94" s="60"/>
-      <c r="D94" s="60"/>
-      <c r="E94" s="60"/>
-      <c r="F94" s="60"/>
-      <c r="G94" s="60"/>
-      <c r="H94" s="60"/>
-      <c r="I94" s="62"/>
-      <c r="J94" s="63"/>
-      <c r="K94" s="63"/>
-      <c r="L94" s="63"/>
+      <c r="C94" s="67"/>
+      <c r="D94" s="67"/>
+      <c r="E94" s="67"/>
+      <c r="F94" s="67"/>
+      <c r="G94" s="67"/>
+      <c r="H94" s="67"/>
+      <c r="I94" s="69"/>
+      <c r="J94" s="70"/>
+      <c r="K94" s="70"/>
+      <c r="L94" s="70"/>
     </row>
     <row r="95" ht="16.5" customHeight="1" spans="1:12">
       <c r="A95" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="B95" s="74" t="s">
+      <c r="B95" s="81" t="s">
         <v>118</v>
       </c>
-      <c r="C95" s="75"/>
-      <c r="D95" s="75"/>
-      <c r="E95" s="76"/>
+      <c r="C95" s="82"/>
+      <c r="D95" s="82"/>
+      <c r="E95" s="83"/>
       <c r="F95" s="40"/>
       <c r="G95" s="40"/>
       <c r="H95" s="40"/>
@@ -5983,7 +6120,7 @@
       <c r="A96" s="49">
         <v>1</v>
       </c>
-      <c r="B96" s="65" t="s">
+      <c r="B96" s="72" t="s">
         <v>119</v>
       </c>
       <c r="C96" s="49"/>
@@ -5998,12 +6135,12 @@
         <v>33</v>
       </c>
       <c r="H96" s="49"/>
-      <c r="I96" s="50" t="s">
+      <c r="I96" s="64" t="s">
         <v>120</v>
       </c>
-      <c r="J96" s="58"/>
-      <c r="K96" s="58"/>
-      <c r="L96" s="58"/>
+      <c r="J96" s="65"/>
+      <c r="K96" s="65"/>
+      <c r="L96" s="65"/>
     </row>
     <row r="97" ht="26.5" customHeight="1" spans="1:12">
       <c r="A97" s="40">
@@ -6110,23 +6247,23 @@
       <c r="L100" s="33"/>
     </row>
     <row r="101" s="7" customFormat="1" ht="17.15" customHeight="1" spans="1:12">
-      <c r="A101" s="60"/>
-      <c r="B101" s="61" t="s">
+      <c r="A101" s="67"/>
+      <c r="B101" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="C101" s="60"/>
-      <c r="D101" s="60"/>
-      <c r="E101" s="60"/>
-      <c r="F101" s="60"/>
-      <c r="G101" s="60"/>
-      <c r="H101" s="60"/>
-      <c r="I101" s="62"/>
-      <c r="J101" s="63"/>
-      <c r="K101" s="63"/>
-      <c r="L101" s="63"/>
+      <c r="C101" s="67"/>
+      <c r="D101" s="67"/>
+      <c r="E101" s="67"/>
+      <c r="F101" s="67"/>
+      <c r="G101" s="67"/>
+      <c r="H101" s="67"/>
+      <c r="I101" s="69"/>
+      <c r="J101" s="70"/>
+      <c r="K101" s="70"/>
+      <c r="L101" s="70"/>
     </row>
     <row r="102" ht="17.15" customHeight="1" spans="1:12">
-      <c r="A102" s="86" t="s">
+      <c r="A102" s="93" t="s">
         <v>128</v>
       </c>
       <c r="B102" s="39" t="s">
@@ -6179,33 +6316,33 @@
       <c r="A104" s="40">
         <v>2</v>
       </c>
-      <c r="B104" s="87" t="s">
+      <c r="B104" s="94" t="s">
         <v>132</v>
       </c>
       <c r="C104" s="40"/>
       <c r="D104" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E104" s="88">
+      <c r="E104" s="95">
         <v>160</v>
       </c>
       <c r="F104" s="40">
         <f t="shared" ref="F104:F123" si="14">C104*E104</f>
         <v>0</v>
       </c>
-      <c r="G104" s="88">
+      <c r="G104" s="95">
         <v>125</v>
       </c>
       <c r="H104" s="40">
         <f t="shared" ref="H104:H123" si="15">SUM(G104*C104)</f>
         <v>0</v>
       </c>
-      <c r="I104" s="89" t="s">
+      <c r="I104" s="96" t="s">
         <v>133</v>
       </c>
-      <c r="J104" s="90"/>
-      <c r="K104" s="90"/>
-      <c r="L104" s="90"/>
+      <c r="J104" s="97"/>
+      <c r="K104" s="97"/>
+      <c r="L104" s="97"/>
     </row>
     <row r="105" ht="14.25" customHeight="1" spans="1:12">
       <c r="A105" s="40">
@@ -6360,7 +6497,7 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="I109" s="91" t="s">
+      <c r="I109" s="98" t="s">
         <v>143</v>
       </c>
       <c r="J109" s="33"/>
@@ -6371,14 +6508,14 @@
       <c r="A110" s="40">
         <v>8</v>
       </c>
-      <c r="B110" s="66" t="s">
+      <c r="B110" s="73" t="s">
         <v>144</v>
       </c>
       <c r="C110" s="40"/>
       <c r="D110" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="E110" s="83">
+      <c r="E110" s="90">
         <v>280</v>
       </c>
       <c r="F110" s="40">
@@ -6392,25 +6529,25 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="I110" s="92" t="s">
+      <c r="I110" s="99" t="s">
         <v>145</v>
       </c>
-      <c r="J110" s="93"/>
-      <c r="K110" s="93"/>
-      <c r="L110" s="93"/>
+      <c r="J110" s="100"/>
+      <c r="K110" s="100"/>
+      <c r="L110" s="100"/>
     </row>
     <row r="111" s="13" customFormat="1" ht="14.25" customHeight="1" spans="1:12">
       <c r="A111" s="40">
         <v>9</v>
       </c>
-      <c r="B111" s="66" t="s">
+      <c r="B111" s="73" t="s">
         <v>146</v>
       </c>
       <c r="C111" s="40"/>
       <c r="D111" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="E111" s="83">
+      <c r="E111" s="90">
         <v>105</v>
       </c>
       <c r="F111" s="40">
@@ -6424,25 +6561,25 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="I111" s="92" t="s">
+      <c r="I111" s="99" t="s">
         <v>147</v>
       </c>
-      <c r="J111" s="93"/>
-      <c r="K111" s="93"/>
-      <c r="L111" s="93"/>
+      <c r="J111" s="100"/>
+      <c r="K111" s="100"/>
+      <c r="L111" s="100"/>
     </row>
     <row r="112" customFormat="1" ht="14.25" customHeight="1" spans="1:12">
       <c r="A112" s="40">
         <v>10</v>
       </c>
-      <c r="B112" s="94" t="s">
+      <c r="B112" s="101" t="s">
         <v>148</v>
       </c>
       <c r="C112" s="40"/>
       <c r="D112" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="E112" s="95">
+      <c r="E112" s="102">
         <v>340</v>
       </c>
       <c r="F112" s="40">
@@ -6456,7 +6593,7 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="I112" s="96" t="s">
+      <c r="I112" s="103" t="s">
         <v>149</v>
       </c>
     </row>
@@ -6464,33 +6601,33 @@
       <c r="A113" s="40">
         <v>11</v>
       </c>
-      <c r="B113" s="97" t="s">
+      <c r="B113" s="104" t="s">
         <v>150</v>
       </c>
       <c r="C113" s="49"/>
       <c r="D113" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="E113" s="82">
+      <c r="E113" s="89">
         <v>25</v>
       </c>
       <c r="F113" s="40">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G113" s="82">
+      <c r="G113" s="89">
         <v>45</v>
       </c>
       <c r="H113" s="40">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="I113" s="57" t="s">
+      <c r="I113" s="63" t="s">
         <v>151</v>
       </c>
-      <c r="J113" s="58"/>
-      <c r="K113" s="58"/>
-      <c r="L113" s="58"/>
+      <c r="J113" s="65"/>
+      <c r="K113" s="65"/>
+      <c r="L113" s="65"/>
     </row>
     <row r="114" ht="14.25" customHeight="1" spans="1:12">
       <c r="A114" s="40">
@@ -6528,28 +6665,28 @@
       <c r="A115" s="40">
         <v>13</v>
       </c>
-      <c r="B115" s="98" t="s">
+      <c r="B115" s="105" t="s">
         <v>154</v>
       </c>
       <c r="C115" s="40"/>
-      <c r="D115" s="99" t="s">
+      <c r="D115" s="106" t="s">
         <v>15</v>
       </c>
-      <c r="E115" s="100">
+      <c r="E115" s="107">
         <v>25</v>
       </c>
       <c r="F115" s="40">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G115" s="100">
+      <c r="G115" s="107">
         <v>48</v>
       </c>
       <c r="H115" s="40">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="I115" s="101" t="s">
+      <c r="I115" s="108" t="s">
         <v>155</v>
       </c>
     </row>
@@ -6557,28 +6694,28 @@
       <c r="A116" s="40">
         <v>14</v>
       </c>
-      <c r="B116" s="98" t="s">
+      <c r="B116" s="105" t="s">
         <v>156</v>
       </c>
-      <c r="C116" s="99"/>
-      <c r="D116" s="99" t="s">
+      <c r="C116" s="106"/>
+      <c r="D116" s="106" t="s">
         <v>15</v>
       </c>
-      <c r="E116" s="100">
+      <c r="E116" s="107">
         <v>65</v>
       </c>
       <c r="F116" s="40">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G116" s="100">
+      <c r="G116" s="107">
         <v>100</v>
       </c>
       <c r="H116" s="40">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="I116" s="101" t="s">
+      <c r="I116" s="108" t="s">
         <v>157</v>
       </c>
       <c r="J116"/>
@@ -6589,7 +6726,7 @@
       <c r="A117" s="40">
         <v>15</v>
       </c>
-      <c r="B117" s="102" t="s">
+      <c r="B117" s="109" t="s">
         <v>158</v>
       </c>
       <c r="C117" s="40"/>
@@ -6642,7 +6779,7 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="I118" s="91" t="s">
+      <c r="I118" s="98" t="s">
         <v>161</v>
       </c>
       <c r="J118" s="33"/>
@@ -6653,33 +6790,33 @@
       <c r="A119" s="40">
         <v>17</v>
       </c>
-      <c r="B119" s="103" t="s">
+      <c r="B119" s="110" t="s">
         <v>162</v>
       </c>
       <c r="C119" s="40"/>
       <c r="D119" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E119" s="104">
+      <c r="E119" s="111">
         <v>9.5</v>
       </c>
       <c r="F119" s="40">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G119" s="104">
+      <c r="G119" s="111">
         <v>6</v>
       </c>
       <c r="H119" s="40">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="I119" s="105" t="s">
+      <c r="I119" s="112" t="s">
         <v>163</v>
       </c>
-      <c r="J119" s="106"/>
-      <c r="K119" s="106"/>
-      <c r="L119" s="106"/>
+      <c r="J119" s="113"/>
+      <c r="K119" s="113"/>
+      <c r="L119" s="113"/>
     </row>
     <row r="120" s="12" customFormat="1" ht="14.25" customHeight="1" spans="1:12">
       <c r="A120" s="40">
@@ -6781,7 +6918,7 @@
       <c r="A123" s="40">
         <v>21</v>
       </c>
-      <c r="B123" s="66" t="s">
+      <c r="B123" s="73" t="s">
         <v>169</v>
       </c>
       <c r="C123" s="40"/>
@@ -6805,46 +6942,46 @@
       <c r="I123" s="41" t="s">
         <v>170</v>
       </c>
-      <c r="J123" s="67"/>
-      <c r="K123" s="67"/>
-      <c r="L123" s="67"/>
+      <c r="J123" s="74"/>
+      <c r="K123" s="74"/>
+      <c r="L123" s="74"/>
     </row>
     <row r="124" s="7" customFormat="1" ht="17.25" customHeight="1" spans="1:12">
-      <c r="A124" s="60"/>
-      <c r="B124" s="61" t="s">
+      <c r="A124" s="67"/>
+      <c r="B124" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="C124" s="60"/>
-      <c r="D124" s="60"/>
-      <c r="E124" s="60"/>
-      <c r="F124" s="60">
+      <c r="C124" s="67"/>
+      <c r="D124" s="67"/>
+      <c r="E124" s="67"/>
+      <c r="F124" s="67">
         <f>SUM(F103:F123)</f>
         <v>0</v>
       </c>
-      <c r="G124" s="60"/>
-      <c r="H124" s="60">
+      <c r="G124" s="67"/>
+      <c r="H124" s="67">
         <f>SUM(H103:H123)</f>
         <v>0</v>
       </c>
-      <c r="I124" s="62"/>
-      <c r="J124" s="63"/>
-      <c r="K124" s="63"/>
-      <c r="L124" s="63"/>
+      <c r="I124" s="69"/>
+      <c r="J124" s="70"/>
+      <c r="K124" s="70"/>
+      <c r="L124" s="70"/>
     </row>
     <row r="125" ht="17.25" customHeight="1" spans="1:12">
       <c r="A125" s="40"/>
-      <c r="B125" s="64" t="s">
+      <c r="B125" s="71" t="s">
         <v>171</v>
       </c>
       <c r="C125" s="40"/>
       <c r="D125" s="40"/>
       <c r="E125" s="40"/>
-      <c r="F125" s="107">
+      <c r="F125" s="114">
         <f>F124+F76+F70+F63+F52+F45+F34+F25</f>
         <v>0</v>
       </c>
-      <c r="G125" s="107"/>
-      <c r="H125" s="107">
+      <c r="G125" s="114"/>
+      <c r="H125" s="114">
         <f>H124+H76+H70+H63+H52+H45+H34+H25</f>
         <v>0</v>
       </c>
@@ -6854,51 +6991,51 @@
       <c r="L125" s="33"/>
     </row>
     <row r="126" s="7" customFormat="1" ht="17.25" customHeight="1" spans="1:12">
-      <c r="A126" s="60"/>
-      <c r="B126" s="61" t="s">
+      <c r="A126" s="67"/>
+      <c r="B126" s="68" t="s">
         <v>172</v>
       </c>
-      <c r="C126" s="60"/>
-      <c r="D126" s="60"/>
-      <c r="E126" s="60"/>
-      <c r="F126" s="60"/>
-      <c r="G126" s="60"/>
-      <c r="H126" s="108">
+      <c r="C126" s="67"/>
+      <c r="D126" s="67"/>
+      <c r="E126" s="67"/>
+      <c r="F126" s="67"/>
+      <c r="G126" s="67"/>
+      <c r="H126" s="115">
         <f>F125+H125</f>
         <v>0</v>
       </c>
-      <c r="I126" s="109"/>
-      <c r="J126" s="63"/>
-      <c r="K126" s="63"/>
-      <c r="L126" s="63"/>
+      <c r="I126" s="116"/>
+      <c r="J126" s="70"/>
+      <c r="K126" s="70"/>
+      <c r="L126" s="70"/>
     </row>
     <row r="127" s="15" customFormat="1" ht="18" customHeight="1" spans="1:12">
-      <c r="A127" s="110"/>
-      <c r="B127" s="111" t="s">
+      <c r="A127" s="117"/>
+      <c r="B127" s="118" t="s">
         <v>173</v>
       </c>
-      <c r="C127" s="112"/>
-      <c r="D127" s="112"/>
-      <c r="E127" s="112"/>
-      <c r="F127" s="112"/>
-      <c r="G127" s="112"/>
-      <c r="H127" s="112"/>
-      <c r="I127" s="113"/>
-      <c r="J127" s="114"/>
-      <c r="K127" s="114"/>
-      <c r="L127" s="114"/>
+      <c r="C127" s="119"/>
+      <c r="D127" s="119"/>
+      <c r="E127" s="119"/>
+      <c r="F127" s="119"/>
+      <c r="G127" s="119"/>
+      <c r="H127" s="119"/>
+      <c r="I127" s="120"/>
+      <c r="J127" s="121"/>
+      <c r="K127" s="121"/>
+      <c r="L127" s="121"/>
     </row>
     <row r="128" ht="14.25" customHeight="1" spans="1:12">
       <c r="A128" s="40"/>
-      <c r="B128" s="115" t="s">
+      <c r="B128" s="122" t="s">
         <v>174</v>
       </c>
       <c r="C128" s="40"/>
       <c r="D128" s="40"/>
       <c r="E128" s="40"/>
       <c r="F128" s="40"/>
-      <c r="G128" s="116"/>
-      <c r="H128" s="107">
+      <c r="G128" s="123"/>
+      <c r="H128" s="114">
         <f>H126*3.5%</f>
         <v>0</v>
       </c>
@@ -6909,17 +7046,17 @@
       <c r="K128" s="33"/>
       <c r="L128" s="33"/>
     </row>
-    <row r="129" ht="24" customHeight="1" spans="1:12">
+    <row r="129" ht="24" customHeight="1" spans="1:24">
       <c r="A129" s="40"/>
-      <c r="B129" s="64" t="s">
+      <c r="B129" s="71" t="s">
         <v>176</v>
       </c>
       <c r="C129" s="40"/>
       <c r="D129" s="40"/>
       <c r="E129" s="40"/>
       <c r="F129" s="40"/>
-      <c r="G129" s="116"/>
-      <c r="H129" s="107">
+      <c r="G129" s="123"/>
+      <c r="H129" s="114">
         <f>H126*3%</f>
         <v>0</v>
       </c>
@@ -6930,103 +7067,164 @@
       <c r="K129" s="33"/>
       <c r="L129" s="33"/>
     </row>
-    <row r="130" s="5" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
+    <row r="130" s="5" customFormat="1" ht="15.75" customHeight="1" spans="1:24">
       <c r="A130" s="40"/>
-      <c r="B130" s="64" t="s">
+      <c r="B130" s="71" t="s">
         <v>178</v>
       </c>
       <c r="C130" s="40"/>
       <c r="D130" s="40"/>
       <c r="E130" s="40"/>
-      <c r="F130" s="117"/>
+      <c r="F130" s="124"/>
       <c r="G130" s="40"/>
-      <c r="H130" s="107">
+      <c r="H130" s="114">
         <f>H126*8%</f>
         <v>0</v>
       </c>
-      <c r="I130" s="41" t="s">
+      <c r="I130" s="54" t="s">
         <v>179</v>
       </c>
-      <c r="J130" s="118"/>
-      <c r="K130" s="119"/>
-      <c r="L130" s="119"/>
-    </row>
-    <row r="131" s="5" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
+      <c r="J130" s="125"/>
+      <c r="K130" s="125"/>
+      <c r="L130" s="125"/>
+      <c r="M130" s="59"/>
+      <c r="N130" s="59"/>
+      <c r="O130" s="59"/>
+      <c r="P130" s="59"/>
+      <c r="Q130" s="59"/>
+      <c r="R130" s="59"/>
+      <c r="S130" s="59"/>
+      <c r="T130" s="59"/>
+      <c r="U130" s="59"/>
+      <c r="V130" s="59"/>
+      <c r="W130" s="59"/>
+      <c r="X130" s="60"/>
+    </row>
+    <row r="131" s="5" customFormat="1" ht="15.75" customHeight="1" spans="1:24">
       <c r="A131" s="40"/>
-      <c r="B131" s="64" t="s">
+      <c r="B131" s="71" t="s">
         <v>180</v>
       </c>
       <c r="C131" s="40"/>
       <c r="D131" s="40"/>
       <c r="E131" s="40"/>
-      <c r="F131" s="117"/>
+      <c r="F131" s="124"/>
       <c r="G131" s="40"/>
-      <c r="H131" s="107">
+      <c r="H131" s="114">
         <f>H126*5%</f>
         <v>0</v>
       </c>
-      <c r="I131" s="41" t="s">
+      <c r="I131" s="54" t="s">
         <v>181</v>
       </c>
-      <c r="J131" s="118"/>
-      <c r="K131" s="119"/>
-      <c r="L131" s="119"/>
-    </row>
-    <row r="132" s="16" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A132" s="110"/>
-      <c r="B132" s="120" t="s">
+      <c r="J131" s="125"/>
+      <c r="K131" s="125"/>
+      <c r="L131" s="125"/>
+      <c r="M131" s="59"/>
+      <c r="N131" s="59"/>
+      <c r="O131" s="59"/>
+      <c r="P131" s="59"/>
+      <c r="Q131" s="59"/>
+      <c r="R131" s="59"/>
+      <c r="S131" s="59"/>
+      <c r="T131" s="59"/>
+      <c r="U131" s="59"/>
+      <c r="V131" s="59"/>
+      <c r="W131" s="59"/>
+      <c r="X131" s="60"/>
+    </row>
+    <row r="132" s="16" customFormat="1" ht="15.75" customHeight="1" spans="1:24">
+      <c r="A132" s="117"/>
+      <c r="B132" s="126" t="s">
         <v>182</v>
       </c>
-      <c r="C132" s="110"/>
-      <c r="D132" s="110"/>
-      <c r="E132" s="110"/>
-      <c r="F132" s="121"/>
-      <c r="G132" s="110"/>
-      <c r="H132" s="122">
+      <c r="C132" s="117"/>
+      <c r="D132" s="117"/>
+      <c r="E132" s="117"/>
+      <c r="F132" s="127"/>
+      <c r="G132" s="117"/>
+      <c r="H132" s="128">
         <f>H131+H130+H129+H128+H126</f>
         <v>0</v>
       </c>
-      <c r="I132" s="123"/>
-      <c r="J132" s="124"/>
-      <c r="K132" s="125"/>
-      <c r="L132" s="125"/>
-    </row>
-    <row r="133" s="5" customFormat="1" ht="15" customHeight="1" spans="1:12">
+      <c r="I132" s="129"/>
+      <c r="J132" s="130"/>
+      <c r="K132" s="130"/>
+      <c r="L132" s="130"/>
+      <c r="M132" s="131"/>
+      <c r="N132" s="131"/>
+      <c r="O132" s="131"/>
+      <c r="P132" s="131"/>
+      <c r="Q132" s="131"/>
+      <c r="R132" s="131"/>
+      <c r="S132" s="131"/>
+      <c r="T132" s="131"/>
+      <c r="U132" s="131"/>
+      <c r="V132" s="131"/>
+      <c r="W132" s="131"/>
+      <c r="X132" s="132"/>
+    </row>
+    <row r="133" s="5" customFormat="1" ht="15" customHeight="1" spans="1:24">
       <c r="A133" s="40"/>
-      <c r="B133" s="126" t="s">
+      <c r="B133" s="133" t="s">
         <v>183</v>
       </c>
-      <c r="C133" s="127"/>
-      <c r="D133" s="127"/>
-      <c r="E133" s="127"/>
-      <c r="F133" s="127"/>
-      <c r="G133" s="127"/>
-      <c r="H133" s="128"/>
-      <c r="I133" s="129" t="s">
+      <c r="C133" s="134"/>
+      <c r="D133" s="134"/>
+      <c r="E133" s="134"/>
+      <c r="F133" s="134"/>
+      <c r="G133" s="134"/>
+      <c r="H133" s="135"/>
+      <c r="I133" s="136" t="s">
         <v>184</v>
       </c>
-      <c r="J133" s="118"/>
-      <c r="K133" s="119"/>
-      <c r="L133" s="119"/>
-    </row>
-    <row r="134" s="16" customFormat="1" ht="17.15" customHeight="1" spans="1:12">
-      <c r="A134" s="110" t="s">
+      <c r="J133" s="125"/>
+      <c r="K133" s="125"/>
+      <c r="L133" s="125"/>
+      <c r="M133" s="59"/>
+      <c r="N133" s="59"/>
+      <c r="O133" s="59"/>
+      <c r="P133" s="59"/>
+      <c r="Q133" s="59"/>
+      <c r="R133" s="59"/>
+      <c r="S133" s="59"/>
+      <c r="T133" s="59"/>
+      <c r="U133" s="59"/>
+      <c r="V133" s="59"/>
+      <c r="W133" s="59"/>
+      <c r="X133" s="60"/>
+    </row>
+    <row r="134" s="16" customFormat="1" ht="17.15" customHeight="1" spans="1:24">
+      <c r="A134" s="117" t="s">
         <v>12</v>
       </c>
-      <c r="B134" s="120" t="s">
+      <c r="B134" s="126" t="s">
         <v>185</v>
       </c>
-      <c r="C134" s="110"/>
-      <c r="D134" s="110"/>
-      <c r="E134" s="110"/>
-      <c r="F134" s="121"/>
-      <c r="G134" s="110"/>
-      <c r="H134" s="121"/>
-      <c r="J134" s="124"/>
-      <c r="K134" s="125"/>
-      <c r="L134" s="125"/>
-    </row>
-    <row r="135" s="5" customFormat="1" ht="15" customHeight="1" spans="1:12">
+      <c r="C134" s="117"/>
+      <c r="D134" s="117"/>
+      <c r="E134" s="117"/>
+      <c r="F134" s="127"/>
+      <c r="G134" s="117"/>
+      <c r="H134" s="127"/>
+      <c r="I134" s="137"/>
+      <c r="J134" s="130"/>
+      <c r="K134" s="130"/>
+      <c r="L134" s="130"/>
+      <c r="M134" s="131"/>
+      <c r="N134" s="131"/>
+      <c r="O134" s="131"/>
+      <c r="P134" s="131"/>
+      <c r="Q134" s="131"/>
+      <c r="R134" s="131"/>
+      <c r="S134" s="131"/>
+      <c r="T134" s="131"/>
+      <c r="U134" s="131"/>
+      <c r="V134" s="131"/>
+      <c r="W134" s="131"/>
+      <c r="X134" s="132"/>
+    </row>
+    <row r="135" s="5" customFormat="1" ht="15" customHeight="1" spans="1:24">
       <c r="A135" s="40">
         <v>1</v>
       </c>
@@ -7045,14 +7243,26 @@
         <v>45</v>
       </c>
       <c r="H135" s="44"/>
-      <c r="I135" s="41" t="s">
+      <c r="I135" s="54" t="s">
         <v>188</v>
       </c>
-      <c r="J135" s="118"/>
-      <c r="K135" s="119"/>
-      <c r="L135" s="119"/>
-    </row>
-    <row r="136" ht="15" customHeight="1" spans="1:12">
+      <c r="J135" s="125"/>
+      <c r="K135" s="125"/>
+      <c r="L135" s="125"/>
+      <c r="M135" s="59"/>
+      <c r="N135" s="59"/>
+      <c r="O135" s="59"/>
+      <c r="P135" s="59"/>
+      <c r="Q135" s="59"/>
+      <c r="R135" s="59"/>
+      <c r="S135" s="59"/>
+      <c r="T135" s="59"/>
+      <c r="U135" s="59"/>
+      <c r="V135" s="59"/>
+      <c r="W135" s="59"/>
+      <c r="X135" s="60"/>
+    </row>
+    <row r="136" ht="15" customHeight="1" spans="1:24">
       <c r="A136" s="40">
         <v>2</v>
       </c>
@@ -7078,7 +7288,7 @@
       <c r="K136" s="33"/>
       <c r="L136" s="33"/>
     </row>
-    <row r="137" ht="15" customHeight="1" spans="1:12">
+    <row r="137" ht="15" customHeight="1" spans="1:24">
       <c r="A137" s="40">
         <v>3</v>
       </c>
@@ -7097,14 +7307,14 @@
         <v>45</v>
       </c>
       <c r="H137" s="40"/>
-      <c r="I137" s="91" t="s">
+      <c r="I137" s="98" t="s">
         <v>192</v>
       </c>
       <c r="J137" s="33"/>
       <c r="K137" s="33"/>
       <c r="L137" s="33"/>
     </row>
-    <row r="138" ht="15" customHeight="1" spans="1:12">
+    <row r="138" ht="15" customHeight="1" spans="1:24">
       <c r="A138" s="40">
         <v>4</v>
       </c>
@@ -7123,14 +7333,14 @@
         <v>60</v>
       </c>
       <c r="H138" s="40"/>
-      <c r="I138" s="91" t="s">
+      <c r="I138" s="98" t="s">
         <v>194</v>
       </c>
       <c r="J138" s="33"/>
       <c r="K138" s="33"/>
       <c r="L138" s="33"/>
     </row>
-    <row r="139" ht="15" customHeight="1" spans="1:12">
+    <row r="139" ht="15" customHeight="1" spans="1:24">
       <c r="A139" s="40">
         <v>5</v>
       </c>
@@ -7149,14 +7359,14 @@
         <v>85</v>
       </c>
       <c r="H139" s="40"/>
-      <c r="I139" s="91" t="s">
+      <c r="I139" s="98" t="s">
         <v>196</v>
       </c>
       <c r="J139" s="33"/>
       <c r="K139" s="33"/>
       <c r="L139" s="33"/>
     </row>
-    <row r="140" ht="15" customHeight="1" spans="1:12">
+    <row r="140" ht="15" customHeight="1" spans="1:24">
       <c r="A140" s="40">
         <v>6</v>
       </c>
@@ -7175,14 +7385,14 @@
         <v>90</v>
       </c>
       <c r="H140" s="40"/>
-      <c r="I140" s="91" t="s">
+      <c r="I140" s="98" t="s">
         <v>161</v>
       </c>
       <c r="J140" s="33"/>
       <c r="K140" s="33"/>
       <c r="L140" s="33"/>
     </row>
-    <row r="141" ht="15" customHeight="1" spans="1:12">
+    <row r="141" ht="15" customHeight="1" spans="1:24">
       <c r="A141" s="40">
         <v>7</v>
       </c>
@@ -7208,7 +7418,7 @@
       <c r="K141" s="33"/>
       <c r="L141" s="33"/>
     </row>
-    <row r="142" ht="15" customHeight="1" spans="1:12">
+    <row r="142" ht="15" customHeight="1" spans="1:24">
       <c r="A142" s="40">
         <v>8</v>
       </c>
@@ -7234,18 +7444,18 @@
       <c r="K142" s="33"/>
       <c r="L142" s="33"/>
     </row>
-    <row r="143" s="13" customFormat="1" ht="15" customHeight="1" spans="1:12">
+    <row r="143" s="13" customFormat="1" ht="15" customHeight="1" spans="1:24">
       <c r="A143" s="40">
         <v>9</v>
       </c>
-      <c r="B143" s="66" t="s">
+      <c r="B143" s="73" t="s">
         <v>199</v>
       </c>
       <c r="C143" s="40"/>
       <c r="D143" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="E143" s="83">
+      <c r="E143" s="90">
         <v>0</v>
       </c>
       <c r="F143" s="40"/>
@@ -7253,25 +7463,25 @@
         <v>50</v>
       </c>
       <c r="H143" s="40"/>
-      <c r="I143" s="92" t="s">
+      <c r="I143" s="99" t="s">
         <v>200</v>
       </c>
-      <c r="J143" s="93"/>
-      <c r="K143" s="93"/>
-      <c r="L143" s="93"/>
-    </row>
-    <row r="144" s="13" customFormat="1" ht="15" customHeight="1" spans="1:12">
+      <c r="J143" s="100"/>
+      <c r="K143" s="100"/>
+      <c r="L143" s="100"/>
+    </row>
+    <row r="144" s="13" customFormat="1" ht="15" customHeight="1" spans="1:24">
       <c r="A144" s="40">
         <v>10</v>
       </c>
-      <c r="B144" s="66" t="s">
+      <c r="B144" s="73" t="s">
         <v>201</v>
       </c>
       <c r="C144" s="40"/>
       <c r="D144" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="E144" s="83">
+      <c r="E144" s="90">
         <v>50</v>
       </c>
       <c r="F144" s="40"/>
@@ -7279,18 +7489,18 @@
         <v>100</v>
       </c>
       <c r="H144" s="40"/>
-      <c r="I144" s="92" t="s">
+      <c r="I144" s="99" t="s">
         <v>202</v>
       </c>
-      <c r="J144" s="93"/>
-      <c r="K144" s="93"/>
-      <c r="L144" s="93"/>
-    </row>
-    <row r="145" ht="15" customHeight="1" spans="1:12">
+      <c r="J144" s="100"/>
+      <c r="K144" s="100"/>
+      <c r="L144" s="100"/>
+    </row>
+    <row r="145" ht="15" customHeight="1" spans="1:171">
       <c r="A145" s="40">
         <v>11</v>
       </c>
-      <c r="B145" s="102" t="s">
+      <c r="B145" s="109" t="s">
         <v>203</v>
       </c>
       <c r="C145" s="40"/>
@@ -7312,59 +7522,59 @@
       <c r="K145" s="33"/>
       <c r="L145" s="33"/>
     </row>
-    <row r="146" s="14" customFormat="1" ht="15" customHeight="1" spans="1:12">
+    <row r="146" s="14" customFormat="1" ht="15" customHeight="1" spans="1:171">
       <c r="A146" s="40">
         <v>12</v>
       </c>
-      <c r="B146" s="97" t="s">
+      <c r="B146" s="104" t="s">
         <v>150</v>
       </c>
       <c r="C146" s="49"/>
       <c r="D146" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="E146" s="82">
+      <c r="E146" s="89">
         <v>25</v>
       </c>
       <c r="F146" s="49"/>
-      <c r="G146" s="82">
+      <c r="G146" s="89">
         <v>45</v>
       </c>
-      <c r="H146" s="82"/>
-      <c r="I146" s="57" t="s">
+      <c r="H146" s="89"/>
+      <c r="I146" s="63" t="s">
         <v>151</v>
       </c>
-      <c r="J146" s="58"/>
-      <c r="K146" s="58"/>
-      <c r="L146" s="58"/>
-    </row>
-    <row r="147" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:12">
+      <c r="J146" s="65"/>
+      <c r="K146" s="65"/>
+      <c r="L146" s="65"/>
+    </row>
+    <row r="147" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:171">
       <c r="A147" s="40">
         <v>13</v>
       </c>
-      <c r="B147" s="57" t="s">
+      <c r="B147" s="63" t="s">
         <v>204</v>
       </c>
       <c r="C147" s="49"/>
       <c r="D147" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="E147" s="82">
+      <c r="E147" s="89">
         <v>23</v>
       </c>
       <c r="F147" s="49"/>
-      <c r="G147" s="82">
+      <c r="G147" s="89">
         <v>16</v>
       </c>
       <c r="H147" s="49"/>
-      <c r="I147" s="50" t="s">
+      <c r="I147" s="64" t="s">
         <v>205</v>
       </c>
-      <c r="J147" s="77"/>
-      <c r="K147" s="77"/>
-      <c r="L147" s="77"/>
-    </row>
-    <row r="148" s="8" customFormat="1" ht="14.15" customHeight="1" spans="1:12">
+      <c r="J147" s="84"/>
+      <c r="K147" s="84"/>
+      <c r="L147" s="84"/>
+    </row>
+    <row r="148" s="8" customFormat="1" ht="14.15" customHeight="1" spans="1:171">
       <c r="A148" s="40">
         <v>14</v>
       </c>
@@ -7386,58 +7596,58 @@
       <c r="I148" s="41" t="s">
         <v>207</v>
       </c>
-      <c r="J148" s="67"/>
-      <c r="K148" s="67"/>
-      <c r="L148" s="67"/>
-    </row>
-    <row r="149" s="8" customFormat="1" ht="14.15" customHeight="1" spans="1:12">
+      <c r="J148" s="74"/>
+      <c r="K148" s="74"/>
+      <c r="L148" s="74"/>
+    </row>
+    <row r="149" s="8" customFormat="1" ht="14.15" customHeight="1" spans="1:171">
       <c r="A149" s="40">
         <v>15</v>
       </c>
-      <c r="B149" s="98" t="s">
+      <c r="B149" s="105" t="s">
         <v>156</v>
       </c>
-      <c r="C149" s="99"/>
-      <c r="D149" s="99" t="s">
+      <c r="C149" s="106"/>
+      <c r="D149" s="106" t="s">
         <v>15</v>
       </c>
-      <c r="E149" s="100">
+      <c r="E149" s="107">
         <v>65</v>
       </c>
       <c r="F149" s="40"/>
-      <c r="G149" s="100">
+      <c r="G149" s="107">
         <v>100</v>
       </c>
       <c r="H149" s="40"/>
-      <c r="I149" s="101" t="s">
+      <c r="I149" s="108" t="s">
         <v>157</v>
       </c>
       <c r="J149"/>
       <c r="K149"/>
       <c r="L149"/>
     </row>
-    <row r="150" s="17" customFormat="1" ht="15" customHeight="1" spans="1:12">
+    <row r="150" s="17" customFormat="1" ht="15" customHeight="1" spans="1:171">
       <c r="A150" s="40">
         <v>16</v>
       </c>
-      <c r="B150" s="130" t="s">
+      <c r="B150" s="138" t="s">
         <v>208</v>
       </c>
       <c r="C150" s="40"/>
       <c r="D150" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E150" s="131"/>
+      <c r="E150" s="139"/>
       <c r="F150" s="40"/>
-      <c r="G150" s="131">
+      <c r="G150" s="139">
         <v>5</v>
       </c>
       <c r="H150" s="40"/>
-      <c r="I150" s="132" t="s">
+      <c r="I150" s="140" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="151" ht="15" customHeight="1" spans="1:12">
+    <row r="151" ht="15" customHeight="1" spans="1:171">
       <c r="A151" s="40">
         <v>17</v>
       </c>
@@ -7463,7 +7673,7 @@
       <c r="K151" s="33"/>
       <c r="L151" s="33"/>
     </row>
-    <row r="152" customFormat="1" ht="15" customHeight="1" spans="1:12">
+    <row r="152" customFormat="1" ht="15" customHeight="1" spans="1:171">
       <c r="A152" s="40">
         <v>18</v>
       </c>
@@ -7489,7 +7699,7 @@
       <c r="K152" s="33"/>
       <c r="L152" s="33"/>
     </row>
-    <row r="153" customFormat="1" ht="15" customHeight="1" spans="1:12">
+    <row r="153" customFormat="1" ht="15" customHeight="1" spans="1:171">
       <c r="A153" s="40">
         <v>19</v>
       </c>
@@ -7515,57 +7725,57 @@
       <c r="K153" s="33"/>
       <c r="L153" s="33"/>
     </row>
-    <row r="154" s="12" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
+    <row r="154" s="12" customFormat="1" ht="15.75" customHeight="1" spans="1:171">
       <c r="A154" s="40">
         <v>20</v>
       </c>
-      <c r="B154" s="133" t="s">
+      <c r="B154" s="141" t="s">
         <v>216</v>
       </c>
       <c r="C154" s="40"/>
-      <c r="D154" s="99" t="s">
+      <c r="D154" s="106" t="s">
         <v>217</v>
       </c>
-      <c r="E154" s="100">
+      <c r="E154" s="107">
         <v>4</v>
       </c>
-      <c r="F154" s="99"/>
-      <c r="G154" s="100">
+      <c r="F154" s="106"/>
+      <c r="G154" s="107">
         <v>2.5</v>
       </c>
       <c r="H154" s="40"/>
-      <c r="I154" s="101" t="s">
+      <c r="I154" s="108" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="155" s="12" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
+    <row r="155" s="12" customFormat="1" ht="15.75" customHeight="1" spans="1:171">
       <c r="A155" s="40">
         <v>21</v>
       </c>
-      <c r="B155" s="98" t="s">
+      <c r="B155" s="105" t="s">
         <v>154</v>
       </c>
       <c r="C155" s="40"/>
-      <c r="D155" s="99" t="s">
+      <c r="D155" s="106" t="s">
         <v>15</v>
       </c>
-      <c r="E155" s="100">
+      <c r="E155" s="107">
         <v>25</v>
       </c>
       <c r="F155" s="40"/>
-      <c r="G155" s="100">
+      <c r="G155" s="107">
         <v>48</v>
       </c>
       <c r="H155" s="40"/>
-      <c r="I155" s="101" t="s">
+      <c r="I155" s="108" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="156" ht="15" customHeight="1" spans="1:12">
+    <row r="156" ht="15" customHeight="1" spans="1:171">
       <c r="A156" s="40">
         <v>22</v>
       </c>
-      <c r="B156" s="102" t="s">
+      <c r="B156" s="109" t="s">
         <v>158</v>
       </c>
       <c r="C156" s="40"/>
@@ -7587,23 +7797,23 @@
       <c r="K156" s="33"/>
       <c r="L156" s="33"/>
     </row>
-    <row r="157" s="8" customFormat="1" ht="14.15" customHeight="1" spans="1:12">
+    <row r="157" s="8" customFormat="1" ht="14.15" customHeight="1" spans="1:171">
       <c r="A157" s="40">
         <v>23</v>
       </c>
-      <c r="B157" s="98" t="s">
+      <c r="B157" s="105" t="s">
         <v>219</v>
       </c>
-      <c r="C157" s="99"/>
-      <c r="D157" s="99" t="s">
+      <c r="C157" s="106"/>
+      <c r="D157" s="106" t="s">
         <v>15</v>
       </c>
-      <c r="E157" s="100"/>
+      <c r="E157" s="107"/>
       <c r="F157" s="40">
         <f>C157*E157</f>
         <v>0</v>
       </c>
-      <c r="G157" s="100">
+      <c r="G157" s="107">
         <v>85</v>
       </c>
       <c r="H157" s="40">
@@ -7615,43 +7825,361 @@
       </c>
       <c r="J157"/>
     </row>
-    <row r="158" s="5" customFormat="1" ht="17.15" customHeight="1" spans="1:12">
+    <row r="158" s="5" customFormat="1" ht="17.15" customHeight="1" spans="1:171">
       <c r="A158" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="B158" s="64" t="s">
+      <c r="B158" s="71" t="s">
         <v>221</v>
       </c>
-      <c r="C158" s="134"/>
-      <c r="D158" s="134"/>
-      <c r="E158" s="134"/>
-      <c r="F158" s="134"/>
-      <c r="G158" s="134"/>
-      <c r="H158" s="134"/>
-      <c r="I158" s="134"/>
-      <c r="J158" s="118"/>
-      <c r="K158" s="119"/>
-      <c r="L158" s="119"/>
-    </row>
-    <row r="159" s="5" customFormat="1" ht="27" customHeight="1" spans="1:12">
+      <c r="C158" s="142"/>
+      <c r="D158" s="142"/>
+      <c r="E158" s="142"/>
+      <c r="F158" s="142"/>
+      <c r="G158" s="142"/>
+      <c r="H158" s="142"/>
+      <c r="I158" s="143"/>
+      <c r="J158" s="125"/>
+      <c r="K158" s="125"/>
+      <c r="L158" s="125"/>
+      <c r="M158" s="59"/>
+      <c r="N158" s="59"/>
+      <c r="O158" s="59"/>
+      <c r="P158" s="59"/>
+      <c r="Q158" s="59"/>
+      <c r="R158" s="59"/>
+      <c r="S158" s="59"/>
+      <c r="T158" s="59"/>
+      <c r="U158" s="59"/>
+      <c r="V158" s="59"/>
+      <c r="W158" s="59"/>
+      <c r="X158" s="59"/>
+      <c r="Y158" s="59"/>
+      <c r="Z158" s="59"/>
+      <c r="AA158" s="59"/>
+      <c r="AB158" s="59"/>
+      <c r="AC158" s="59"/>
+      <c r="AD158" s="59"/>
+      <c r="AE158" s="59"/>
+      <c r="AF158" s="59"/>
+      <c r="AG158" s="59"/>
+      <c r="AH158" s="59"/>
+      <c r="AI158" s="59"/>
+      <c r="AJ158" s="59"/>
+      <c r="AK158" s="59"/>
+      <c r="AL158" s="59"/>
+      <c r="AM158" s="59"/>
+      <c r="AN158" s="59"/>
+      <c r="AO158" s="59"/>
+      <c r="AP158" s="59"/>
+      <c r="AQ158" s="59"/>
+      <c r="AR158" s="59"/>
+      <c r="AS158" s="59"/>
+      <c r="AT158" s="59"/>
+      <c r="AU158" s="59"/>
+      <c r="AV158" s="59"/>
+      <c r="AW158" s="59"/>
+      <c r="AX158" s="59"/>
+      <c r="AY158" s="59"/>
+      <c r="AZ158" s="59"/>
+      <c r="BA158" s="59"/>
+      <c r="BB158" s="59"/>
+      <c r="BC158" s="59"/>
+      <c r="BD158" s="59"/>
+      <c r="BE158" s="59"/>
+      <c r="BF158" s="59"/>
+      <c r="BG158" s="59"/>
+      <c r="BH158" s="59"/>
+      <c r="BI158" s="59"/>
+      <c r="BJ158" s="59"/>
+      <c r="BK158" s="59"/>
+      <c r="BL158" s="59"/>
+      <c r="BM158" s="59"/>
+      <c r="BN158" s="59"/>
+      <c r="BO158" s="59"/>
+      <c r="BP158" s="59"/>
+      <c r="BQ158" s="59"/>
+      <c r="BR158" s="59"/>
+      <c r="BS158" s="59"/>
+      <c r="BT158" s="59"/>
+      <c r="BU158" s="59"/>
+      <c r="BV158" s="59"/>
+      <c r="BW158" s="59"/>
+      <c r="BX158" s="59"/>
+      <c r="BY158" s="59"/>
+      <c r="BZ158" s="59"/>
+      <c r="CA158" s="59"/>
+      <c r="CB158" s="59"/>
+      <c r="CC158" s="59"/>
+      <c r="CD158" s="59"/>
+      <c r="CE158" s="59"/>
+      <c r="CF158" s="59"/>
+      <c r="CG158" s="59"/>
+      <c r="CH158" s="59"/>
+      <c r="CI158" s="59"/>
+      <c r="CJ158" s="59"/>
+      <c r="CK158" s="59"/>
+      <c r="CL158" s="59"/>
+      <c r="CM158" s="59"/>
+      <c r="CN158" s="59"/>
+      <c r="CO158" s="59"/>
+      <c r="CP158" s="59"/>
+      <c r="CQ158" s="59"/>
+      <c r="CR158" s="59"/>
+      <c r="CS158" s="59"/>
+      <c r="CT158" s="59"/>
+      <c r="CU158" s="59"/>
+      <c r="CV158" s="59"/>
+      <c r="CW158" s="59"/>
+      <c r="CX158" s="59"/>
+      <c r="CY158" s="59"/>
+      <c r="CZ158" s="59"/>
+      <c r="DA158" s="59"/>
+      <c r="DB158" s="59"/>
+      <c r="DC158" s="59"/>
+      <c r="DD158" s="59"/>
+      <c r="DE158" s="59"/>
+      <c r="DF158" s="59"/>
+      <c r="DG158" s="59"/>
+      <c r="DH158" s="59"/>
+      <c r="DI158" s="59"/>
+      <c r="DJ158" s="59"/>
+      <c r="DK158" s="59"/>
+      <c r="DL158" s="59"/>
+      <c r="DM158" s="59"/>
+      <c r="DN158" s="59"/>
+      <c r="DO158" s="59"/>
+      <c r="DP158" s="59"/>
+      <c r="DQ158" s="59"/>
+      <c r="DR158" s="59"/>
+      <c r="DS158" s="59"/>
+      <c r="DT158" s="59"/>
+      <c r="DU158" s="59"/>
+      <c r="DV158" s="59"/>
+      <c r="DW158" s="59"/>
+      <c r="DX158" s="59"/>
+      <c r="DY158" s="59"/>
+      <c r="DZ158" s="59"/>
+      <c r="EA158" s="59"/>
+      <c r="EB158" s="59"/>
+      <c r="EC158" s="59"/>
+      <c r="ED158" s="59"/>
+      <c r="EE158" s="59"/>
+      <c r="EF158" s="59"/>
+      <c r="EG158" s="59"/>
+      <c r="EH158" s="59"/>
+      <c r="EI158" s="59"/>
+      <c r="EJ158" s="59"/>
+      <c r="EK158" s="59"/>
+      <c r="EL158" s="59"/>
+      <c r="EM158" s="59"/>
+      <c r="EN158" s="59"/>
+      <c r="EO158" s="59"/>
+      <c r="EP158" s="59"/>
+      <c r="EQ158" s="59"/>
+      <c r="ER158" s="59"/>
+      <c r="ES158" s="59"/>
+      <c r="ET158" s="59"/>
+      <c r="EU158" s="59"/>
+      <c r="EV158" s="59"/>
+      <c r="EW158" s="59"/>
+      <c r="EX158" s="59"/>
+      <c r="EY158" s="59"/>
+      <c r="EZ158" s="59"/>
+      <c r="FA158" s="59"/>
+      <c r="FB158" s="59"/>
+      <c r="FC158" s="59"/>
+      <c r="FD158" s="59"/>
+      <c r="FE158" s="59"/>
+      <c r="FF158" s="59"/>
+      <c r="FG158" s="59"/>
+      <c r="FH158" s="59"/>
+      <c r="FI158" s="59"/>
+      <c r="FJ158" s="59"/>
+      <c r="FK158" s="59"/>
+      <c r="FL158" s="59"/>
+      <c r="FM158" s="59"/>
+      <c r="FN158" s="59"/>
+      <c r="FO158" s="60"/>
+    </row>
+    <row r="159" s="5" customFormat="1" ht="27" customHeight="1" spans="1:171">
       <c r="A159" s="40">
         <v>1</v>
       </c>
-      <c r="B159" s="135" t="s">
+      <c r="B159" s="144" t="s">
         <v>222</v>
       </c>
-      <c r="C159" s="135"/>
-      <c r="D159" s="135"/>
-      <c r="E159" s="135"/>
-      <c r="F159" s="135"/>
-      <c r="G159" s="135"/>
-      <c r="H159" s="135"/>
-      <c r="I159" s="135"/>
-      <c r="J159" s="118"/>
-      <c r="K159" s="119"/>
-      <c r="L159" s="119"/>
-    </row>
-    <row r="160" s="5" customFormat="1" ht="29" customHeight="1" spans="1:12">
+      <c r="C159" s="144"/>
+      <c r="D159" s="144"/>
+      <c r="E159" s="144"/>
+      <c r="F159" s="144"/>
+      <c r="G159" s="144"/>
+      <c r="H159" s="144"/>
+      <c r="I159" s="145"/>
+      <c r="J159" s="125"/>
+      <c r="K159" s="125"/>
+      <c r="L159" s="125"/>
+      <c r="M159" s="59"/>
+      <c r="N159" s="59"/>
+      <c r="O159" s="59"/>
+      <c r="P159" s="59"/>
+      <c r="Q159" s="59"/>
+      <c r="R159" s="59"/>
+      <c r="S159" s="59"/>
+      <c r="T159" s="59"/>
+      <c r="U159" s="59"/>
+      <c r="V159" s="59"/>
+      <c r="W159" s="59"/>
+      <c r="X159" s="59"/>
+      <c r="Y159" s="59"/>
+      <c r="Z159" s="59"/>
+      <c r="AA159" s="59"/>
+      <c r="AB159" s="59"/>
+      <c r="AC159" s="59"/>
+      <c r="AD159" s="59"/>
+      <c r="AE159" s="59"/>
+      <c r="AF159" s="59"/>
+      <c r="AG159" s="59"/>
+      <c r="AH159" s="59"/>
+      <c r="AI159" s="59"/>
+      <c r="AJ159" s="59"/>
+      <c r="AK159" s="59"/>
+      <c r="AL159" s="59"/>
+      <c r="AM159" s="59"/>
+      <c r="AN159" s="59"/>
+      <c r="AO159" s="59"/>
+      <c r="AP159" s="59"/>
+      <c r="AQ159" s="59"/>
+      <c r="AR159" s="59"/>
+      <c r="AS159" s="59"/>
+      <c r="AT159" s="59"/>
+      <c r="AU159" s="59"/>
+      <c r="AV159" s="59"/>
+      <c r="AW159" s="59"/>
+      <c r="AX159" s="59"/>
+      <c r="AY159" s="59"/>
+      <c r="AZ159" s="59"/>
+      <c r="BA159" s="59"/>
+      <c r="BB159" s="59"/>
+      <c r="BC159" s="59"/>
+      <c r="BD159" s="59"/>
+      <c r="BE159" s="59"/>
+      <c r="BF159" s="59"/>
+      <c r="BG159" s="59"/>
+      <c r="BH159" s="59"/>
+      <c r="BI159" s="59"/>
+      <c r="BJ159" s="59"/>
+      <c r="BK159" s="59"/>
+      <c r="BL159" s="59"/>
+      <c r="BM159" s="59"/>
+      <c r="BN159" s="59"/>
+      <c r="BO159" s="59"/>
+      <c r="BP159" s="59"/>
+      <c r="BQ159" s="59"/>
+      <c r="BR159" s="59"/>
+      <c r="BS159" s="59"/>
+      <c r="BT159" s="59"/>
+      <c r="BU159" s="59"/>
+      <c r="BV159" s="59"/>
+      <c r="BW159" s="59"/>
+      <c r="BX159" s="59"/>
+      <c r="BY159" s="59"/>
+      <c r="BZ159" s="59"/>
+      <c r="CA159" s="59"/>
+      <c r="CB159" s="59"/>
+      <c r="CC159" s="59"/>
+      <c r="CD159" s="59"/>
+      <c r="CE159" s="59"/>
+      <c r="CF159" s="59"/>
+      <c r="CG159" s="59"/>
+      <c r="CH159" s="59"/>
+      <c r="CI159" s="59"/>
+      <c r="CJ159" s="59"/>
+      <c r="CK159" s="59"/>
+      <c r="CL159" s="59"/>
+      <c r="CM159" s="59"/>
+      <c r="CN159" s="59"/>
+      <c r="CO159" s="59"/>
+      <c r="CP159" s="59"/>
+      <c r="CQ159" s="59"/>
+      <c r="CR159" s="59"/>
+      <c r="CS159" s="59"/>
+      <c r="CT159" s="59"/>
+      <c r="CU159" s="59"/>
+      <c r="CV159" s="59"/>
+      <c r="CW159" s="59"/>
+      <c r="CX159" s="59"/>
+      <c r="CY159" s="59"/>
+      <c r="CZ159" s="59"/>
+      <c r="DA159" s="59"/>
+      <c r="DB159" s="59"/>
+      <c r="DC159" s="59"/>
+      <c r="DD159" s="59"/>
+      <c r="DE159" s="59"/>
+      <c r="DF159" s="59"/>
+      <c r="DG159" s="59"/>
+      <c r="DH159" s="59"/>
+      <c r="DI159" s="59"/>
+      <c r="DJ159" s="59"/>
+      <c r="DK159" s="59"/>
+      <c r="DL159" s="59"/>
+      <c r="DM159" s="59"/>
+      <c r="DN159" s="59"/>
+      <c r="DO159" s="59"/>
+      <c r="DP159" s="59"/>
+      <c r="DQ159" s="59"/>
+      <c r="DR159" s="59"/>
+      <c r="DS159" s="59"/>
+      <c r="DT159" s="59"/>
+      <c r="DU159" s="59"/>
+      <c r="DV159" s="59"/>
+      <c r="DW159" s="59"/>
+      <c r="DX159" s="59"/>
+      <c r="DY159" s="59"/>
+      <c r="DZ159" s="59"/>
+      <c r="EA159" s="59"/>
+      <c r="EB159" s="59"/>
+      <c r="EC159" s="59"/>
+      <c r="ED159" s="59"/>
+      <c r="EE159" s="59"/>
+      <c r="EF159" s="59"/>
+      <c r="EG159" s="59"/>
+      <c r="EH159" s="59"/>
+      <c r="EI159" s="59"/>
+      <c r="EJ159" s="59"/>
+      <c r="EK159" s="59"/>
+      <c r="EL159" s="59"/>
+      <c r="EM159" s="59"/>
+      <c r="EN159" s="59"/>
+      <c r="EO159" s="59"/>
+      <c r="EP159" s="59"/>
+      <c r="EQ159" s="59"/>
+      <c r="ER159" s="59"/>
+      <c r="ES159" s="59"/>
+      <c r="ET159" s="59"/>
+      <c r="EU159" s="59"/>
+      <c r="EV159" s="59"/>
+      <c r="EW159" s="59"/>
+      <c r="EX159" s="59"/>
+      <c r="EY159" s="59"/>
+      <c r="EZ159" s="59"/>
+      <c r="FA159" s="59"/>
+      <c r="FB159" s="59"/>
+      <c r="FC159" s="59"/>
+      <c r="FD159" s="59"/>
+      <c r="FE159" s="59"/>
+      <c r="FF159" s="59"/>
+      <c r="FG159" s="59"/>
+      <c r="FH159" s="59"/>
+      <c r="FI159" s="59"/>
+      <c r="FJ159" s="59"/>
+      <c r="FK159" s="59"/>
+      <c r="FL159" s="59"/>
+      <c r="FM159" s="59"/>
+      <c r="FN159" s="59"/>
+      <c r="FO159" s="60"/>
+    </row>
+    <row r="160" s="5" customFormat="1" ht="29" customHeight="1" spans="1:171">
       <c r="A160" s="40">
         <v>2</v>
       </c>
@@ -7664,66 +8192,702 @@
       <c r="F160" s="43"/>
       <c r="G160" s="43"/>
       <c r="H160" s="43"/>
-      <c r="I160" s="43"/>
-      <c r="J160" s="118"/>
-      <c r="K160" s="119"/>
-      <c r="L160" s="119"/>
-    </row>
-    <row r="161" s="5" customFormat="1" ht="29.25" customHeight="1" spans="1:12">
+      <c r="I160" s="133"/>
+      <c r="J160" s="125"/>
+      <c r="K160" s="125"/>
+      <c r="L160" s="125"/>
+      <c r="M160" s="59"/>
+      <c r="N160" s="59"/>
+      <c r="O160" s="59"/>
+      <c r="P160" s="59"/>
+      <c r="Q160" s="59"/>
+      <c r="R160" s="59"/>
+      <c r="S160" s="59"/>
+      <c r="T160" s="59"/>
+      <c r="U160" s="59"/>
+      <c r="V160" s="59"/>
+      <c r="W160" s="59"/>
+      <c r="X160" s="59"/>
+      <c r="Y160" s="59"/>
+      <c r="Z160" s="59"/>
+      <c r="AA160" s="59"/>
+      <c r="AB160" s="59"/>
+      <c r="AC160" s="59"/>
+      <c r="AD160" s="59"/>
+      <c r="AE160" s="59"/>
+      <c r="AF160" s="59"/>
+      <c r="AG160" s="59"/>
+      <c r="AH160" s="59"/>
+      <c r="AI160" s="59"/>
+      <c r="AJ160" s="59"/>
+      <c r="AK160" s="59"/>
+      <c r="AL160" s="59"/>
+      <c r="AM160" s="59"/>
+      <c r="AN160" s="59"/>
+      <c r="AO160" s="59"/>
+      <c r="AP160" s="59"/>
+      <c r="AQ160" s="59"/>
+      <c r="AR160" s="59"/>
+      <c r="AS160" s="59"/>
+      <c r="AT160" s="59"/>
+      <c r="AU160" s="59"/>
+      <c r="AV160" s="59"/>
+      <c r="AW160" s="59"/>
+      <c r="AX160" s="59"/>
+      <c r="AY160" s="59"/>
+      <c r="AZ160" s="59"/>
+      <c r="BA160" s="59"/>
+      <c r="BB160" s="59"/>
+      <c r="BC160" s="59"/>
+      <c r="BD160" s="59"/>
+      <c r="BE160" s="59"/>
+      <c r="BF160" s="59"/>
+      <c r="BG160" s="59"/>
+      <c r="BH160" s="59"/>
+      <c r="BI160" s="59"/>
+      <c r="BJ160" s="59"/>
+      <c r="BK160" s="59"/>
+      <c r="BL160" s="59"/>
+      <c r="BM160" s="59"/>
+      <c r="BN160" s="59"/>
+      <c r="BO160" s="59"/>
+      <c r="BP160" s="59"/>
+      <c r="BQ160" s="59"/>
+      <c r="BR160" s="59"/>
+      <c r="BS160" s="59"/>
+      <c r="BT160" s="59"/>
+      <c r="BU160" s="59"/>
+      <c r="BV160" s="59"/>
+      <c r="BW160" s="59"/>
+      <c r="BX160" s="59"/>
+      <c r="BY160" s="59"/>
+      <c r="BZ160" s="59"/>
+      <c r="CA160" s="59"/>
+      <c r="CB160" s="59"/>
+      <c r="CC160" s="59"/>
+      <c r="CD160" s="59"/>
+      <c r="CE160" s="59"/>
+      <c r="CF160" s="59"/>
+      <c r="CG160" s="59"/>
+      <c r="CH160" s="59"/>
+      <c r="CI160" s="59"/>
+      <c r="CJ160" s="59"/>
+      <c r="CK160" s="59"/>
+      <c r="CL160" s="59"/>
+      <c r="CM160" s="59"/>
+      <c r="CN160" s="59"/>
+      <c r="CO160" s="59"/>
+      <c r="CP160" s="59"/>
+      <c r="CQ160" s="59"/>
+      <c r="CR160" s="59"/>
+      <c r="CS160" s="59"/>
+      <c r="CT160" s="59"/>
+      <c r="CU160" s="59"/>
+      <c r="CV160" s="59"/>
+      <c r="CW160" s="59"/>
+      <c r="CX160" s="59"/>
+      <c r="CY160" s="59"/>
+      <c r="CZ160" s="59"/>
+      <c r="DA160" s="59"/>
+      <c r="DB160" s="59"/>
+      <c r="DC160" s="59"/>
+      <c r="DD160" s="59"/>
+      <c r="DE160" s="59"/>
+      <c r="DF160" s="59"/>
+      <c r="DG160" s="59"/>
+      <c r="DH160" s="59"/>
+      <c r="DI160" s="59"/>
+      <c r="DJ160" s="59"/>
+      <c r="DK160" s="59"/>
+      <c r="DL160" s="59"/>
+      <c r="DM160" s="59"/>
+      <c r="DN160" s="59"/>
+      <c r="DO160" s="59"/>
+      <c r="DP160" s="59"/>
+      <c r="DQ160" s="59"/>
+      <c r="DR160" s="59"/>
+      <c r="DS160" s="59"/>
+      <c r="DT160" s="59"/>
+      <c r="DU160" s="59"/>
+      <c r="DV160" s="59"/>
+      <c r="DW160" s="59"/>
+      <c r="DX160" s="59"/>
+      <c r="DY160" s="59"/>
+      <c r="DZ160" s="59"/>
+      <c r="EA160" s="59"/>
+      <c r="EB160" s="59"/>
+      <c r="EC160" s="59"/>
+      <c r="ED160" s="59"/>
+      <c r="EE160" s="59"/>
+      <c r="EF160" s="59"/>
+      <c r="EG160" s="59"/>
+      <c r="EH160" s="59"/>
+      <c r="EI160" s="59"/>
+      <c r="EJ160" s="59"/>
+      <c r="EK160" s="59"/>
+      <c r="EL160" s="59"/>
+      <c r="EM160" s="59"/>
+      <c r="EN160" s="59"/>
+      <c r="EO160" s="59"/>
+      <c r="EP160" s="59"/>
+      <c r="EQ160" s="59"/>
+      <c r="ER160" s="59"/>
+      <c r="ES160" s="59"/>
+      <c r="ET160" s="59"/>
+      <c r="EU160" s="59"/>
+      <c r="EV160" s="59"/>
+      <c r="EW160" s="59"/>
+      <c r="EX160" s="59"/>
+      <c r="EY160" s="59"/>
+      <c r="EZ160" s="59"/>
+      <c r="FA160" s="59"/>
+      <c r="FB160" s="59"/>
+      <c r="FC160" s="59"/>
+      <c r="FD160" s="59"/>
+      <c r="FE160" s="59"/>
+      <c r="FF160" s="59"/>
+      <c r="FG160" s="59"/>
+      <c r="FH160" s="59"/>
+      <c r="FI160" s="59"/>
+      <c r="FJ160" s="59"/>
+      <c r="FK160" s="59"/>
+      <c r="FL160" s="59"/>
+      <c r="FM160" s="59"/>
+      <c r="FN160" s="59"/>
+      <c r="FO160" s="60"/>
+    </row>
+    <row r="161" s="5" customFormat="1" ht="29.25" customHeight="1" spans="1:171">
       <c r="A161" s="40">
         <v>3</v>
       </c>
-      <c r="B161" s="135" t="s">
+      <c r="B161" s="144" t="s">
         <v>224</v>
       </c>
-      <c r="C161" s="135"/>
-      <c r="D161" s="135"/>
-      <c r="E161" s="135"/>
-      <c r="F161" s="135"/>
-      <c r="G161" s="135"/>
-      <c r="H161" s="135"/>
-      <c r="I161" s="135"/>
-      <c r="J161" s="118"/>
-      <c r="K161" s="119"/>
-      <c r="L161" s="119"/>
-    </row>
-    <row r="162" s="5" customFormat="1" ht="27.75" customHeight="1" spans="1:12">
+      <c r="C161" s="144"/>
+      <c r="D161" s="144"/>
+      <c r="E161" s="144"/>
+      <c r="F161" s="144"/>
+      <c r="G161" s="144"/>
+      <c r="H161" s="144"/>
+      <c r="I161" s="145"/>
+      <c r="J161" s="125"/>
+      <c r="K161" s="125"/>
+      <c r="L161" s="125"/>
+      <c r="M161" s="59"/>
+      <c r="N161" s="59"/>
+      <c r="O161" s="59"/>
+      <c r="P161" s="59"/>
+      <c r="Q161" s="59"/>
+      <c r="R161" s="59"/>
+      <c r="S161" s="59"/>
+      <c r="T161" s="59"/>
+      <c r="U161" s="59"/>
+      <c r="V161" s="59"/>
+      <c r="W161" s="59"/>
+      <c r="X161" s="59"/>
+      <c r="Y161" s="59"/>
+      <c r="Z161" s="59"/>
+      <c r="AA161" s="59"/>
+      <c r="AB161" s="59"/>
+      <c r="AC161" s="59"/>
+      <c r="AD161" s="59"/>
+      <c r="AE161" s="59"/>
+      <c r="AF161" s="59"/>
+      <c r="AG161" s="59"/>
+      <c r="AH161" s="59"/>
+      <c r="AI161" s="59"/>
+      <c r="AJ161" s="59"/>
+      <c r="AK161" s="59"/>
+      <c r="AL161" s="59"/>
+      <c r="AM161" s="59"/>
+      <c r="AN161" s="59"/>
+      <c r="AO161" s="59"/>
+      <c r="AP161" s="59"/>
+      <c r="AQ161" s="59"/>
+      <c r="AR161" s="59"/>
+      <c r="AS161" s="59"/>
+      <c r="AT161" s="59"/>
+      <c r="AU161" s="59"/>
+      <c r="AV161" s="59"/>
+      <c r="AW161" s="59"/>
+      <c r="AX161" s="59"/>
+      <c r="AY161" s="59"/>
+      <c r="AZ161" s="59"/>
+      <c r="BA161" s="59"/>
+      <c r="BB161" s="59"/>
+      <c r="BC161" s="59"/>
+      <c r="BD161" s="59"/>
+      <c r="BE161" s="59"/>
+      <c r="BF161" s="59"/>
+      <c r="BG161" s="59"/>
+      <c r="BH161" s="59"/>
+      <c r="BI161" s="59"/>
+      <c r="BJ161" s="59"/>
+      <c r="BK161" s="59"/>
+      <c r="BL161" s="59"/>
+      <c r="BM161" s="59"/>
+      <c r="BN161" s="59"/>
+      <c r="BO161" s="59"/>
+      <c r="BP161" s="59"/>
+      <c r="BQ161" s="59"/>
+      <c r="BR161" s="59"/>
+      <c r="BS161" s="59"/>
+      <c r="BT161" s="59"/>
+      <c r="BU161" s="59"/>
+      <c r="BV161" s="59"/>
+      <c r="BW161" s="59"/>
+      <c r="BX161" s="59"/>
+      <c r="BY161" s="59"/>
+      <c r="BZ161" s="59"/>
+      <c r="CA161" s="59"/>
+      <c r="CB161" s="59"/>
+      <c r="CC161" s="59"/>
+      <c r="CD161" s="59"/>
+      <c r="CE161" s="59"/>
+      <c r="CF161" s="59"/>
+      <c r="CG161" s="59"/>
+      <c r="CH161" s="59"/>
+      <c r="CI161" s="59"/>
+      <c r="CJ161" s="59"/>
+      <c r="CK161" s="59"/>
+      <c r="CL161" s="59"/>
+      <c r="CM161" s="59"/>
+      <c r="CN161" s="59"/>
+      <c r="CO161" s="59"/>
+      <c r="CP161" s="59"/>
+      <c r="CQ161" s="59"/>
+      <c r="CR161" s="59"/>
+      <c r="CS161" s="59"/>
+      <c r="CT161" s="59"/>
+      <c r="CU161" s="59"/>
+      <c r="CV161" s="59"/>
+      <c r="CW161" s="59"/>
+      <c r="CX161" s="59"/>
+      <c r="CY161" s="59"/>
+      <c r="CZ161" s="59"/>
+      <c r="DA161" s="59"/>
+      <c r="DB161" s="59"/>
+      <c r="DC161" s="59"/>
+      <c r="DD161" s="59"/>
+      <c r="DE161" s="59"/>
+      <c r="DF161" s="59"/>
+      <c r="DG161" s="59"/>
+      <c r="DH161" s="59"/>
+      <c r="DI161" s="59"/>
+      <c r="DJ161" s="59"/>
+      <c r="DK161" s="59"/>
+      <c r="DL161" s="59"/>
+      <c r="DM161" s="59"/>
+      <c r="DN161" s="59"/>
+      <c r="DO161" s="59"/>
+      <c r="DP161" s="59"/>
+      <c r="DQ161" s="59"/>
+      <c r="DR161" s="59"/>
+      <c r="DS161" s="59"/>
+      <c r="DT161" s="59"/>
+      <c r="DU161" s="59"/>
+      <c r="DV161" s="59"/>
+      <c r="DW161" s="59"/>
+      <c r="DX161" s="59"/>
+      <c r="DY161" s="59"/>
+      <c r="DZ161" s="59"/>
+      <c r="EA161" s="59"/>
+      <c r="EB161" s="59"/>
+      <c r="EC161" s="59"/>
+      <c r="ED161" s="59"/>
+      <c r="EE161" s="59"/>
+      <c r="EF161" s="59"/>
+      <c r="EG161" s="59"/>
+      <c r="EH161" s="59"/>
+      <c r="EI161" s="59"/>
+      <c r="EJ161" s="59"/>
+      <c r="EK161" s="59"/>
+      <c r="EL161" s="59"/>
+      <c r="EM161" s="59"/>
+      <c r="EN161" s="59"/>
+      <c r="EO161" s="59"/>
+      <c r="EP161" s="59"/>
+      <c r="EQ161" s="59"/>
+      <c r="ER161" s="59"/>
+      <c r="ES161" s="59"/>
+      <c r="ET161" s="59"/>
+      <c r="EU161" s="59"/>
+      <c r="EV161" s="59"/>
+      <c r="EW161" s="59"/>
+      <c r="EX161" s="59"/>
+      <c r="EY161" s="59"/>
+      <c r="EZ161" s="59"/>
+      <c r="FA161" s="59"/>
+      <c r="FB161" s="59"/>
+      <c r="FC161" s="59"/>
+      <c r="FD161" s="59"/>
+      <c r="FE161" s="59"/>
+      <c r="FF161" s="59"/>
+      <c r="FG161" s="59"/>
+      <c r="FH161" s="59"/>
+      <c r="FI161" s="59"/>
+      <c r="FJ161" s="59"/>
+      <c r="FK161" s="59"/>
+      <c r="FL161" s="59"/>
+      <c r="FM161" s="59"/>
+      <c r="FN161" s="59"/>
+      <c r="FO161" s="60"/>
+    </row>
+    <row r="162" s="5" customFormat="1" ht="27.75" customHeight="1" spans="1:171">
       <c r="A162" s="40">
         <v>4</v>
       </c>
-      <c r="B162" s="135" t="s">
+      <c r="B162" s="144" t="s">
         <v>225</v>
       </c>
-      <c r="C162" s="135"/>
-      <c r="D162" s="135"/>
-      <c r="E162" s="135"/>
-      <c r="F162" s="135"/>
-      <c r="G162" s="135"/>
-      <c r="H162" s="135"/>
-      <c r="I162" s="135"/>
-      <c r="J162" s="118"/>
-      <c r="K162" s="119"/>
-      <c r="L162" s="119"/>
-    </row>
-    <row r="163" s="5" customFormat="1" ht="57" customHeight="1" spans="1:12">
+      <c r="C162" s="144"/>
+      <c r="D162" s="144"/>
+      <c r="E162" s="144"/>
+      <c r="F162" s="144"/>
+      <c r="G162" s="144"/>
+      <c r="H162" s="144"/>
+      <c r="I162" s="145"/>
+      <c r="J162" s="125"/>
+      <c r="K162" s="125"/>
+      <c r="L162" s="125"/>
+      <c r="M162" s="59"/>
+      <c r="N162" s="59"/>
+      <c r="O162" s="59"/>
+      <c r="P162" s="59"/>
+      <c r="Q162" s="59"/>
+      <c r="R162" s="59"/>
+      <c r="S162" s="59"/>
+      <c r="T162" s="59"/>
+      <c r="U162" s="59"/>
+      <c r="V162" s="59"/>
+      <c r="W162" s="59"/>
+      <c r="X162" s="59"/>
+      <c r="Y162" s="59"/>
+      <c r="Z162" s="59"/>
+      <c r="AA162" s="59"/>
+      <c r="AB162" s="59"/>
+      <c r="AC162" s="59"/>
+      <c r="AD162" s="59"/>
+      <c r="AE162" s="59"/>
+      <c r="AF162" s="59"/>
+      <c r="AG162" s="59"/>
+      <c r="AH162" s="59"/>
+      <c r="AI162" s="59"/>
+      <c r="AJ162" s="59"/>
+      <c r="AK162" s="59"/>
+      <c r="AL162" s="59"/>
+      <c r="AM162" s="59"/>
+      <c r="AN162" s="59"/>
+      <c r="AO162" s="59"/>
+      <c r="AP162" s="59"/>
+      <c r="AQ162" s="59"/>
+      <c r="AR162" s="59"/>
+      <c r="AS162" s="59"/>
+      <c r="AT162" s="59"/>
+      <c r="AU162" s="59"/>
+      <c r="AV162" s="59"/>
+      <c r="AW162" s="59"/>
+      <c r="AX162" s="59"/>
+      <c r="AY162" s="59"/>
+      <c r="AZ162" s="59"/>
+      <c r="BA162" s="59"/>
+      <c r="BB162" s="59"/>
+      <c r="BC162" s="59"/>
+      <c r="BD162" s="59"/>
+      <c r="BE162" s="59"/>
+      <c r="BF162" s="59"/>
+      <c r="BG162" s="59"/>
+      <c r="BH162" s="59"/>
+      <c r="BI162" s="59"/>
+      <c r="BJ162" s="59"/>
+      <c r="BK162" s="59"/>
+      <c r="BL162" s="59"/>
+      <c r="BM162" s="59"/>
+      <c r="BN162" s="59"/>
+      <c r="BO162" s="59"/>
+      <c r="BP162" s="59"/>
+      <c r="BQ162" s="59"/>
+      <c r="BR162" s="59"/>
+      <c r="BS162" s="59"/>
+      <c r="BT162" s="59"/>
+      <c r="BU162" s="59"/>
+      <c r="BV162" s="59"/>
+      <c r="BW162" s="59"/>
+      <c r="BX162" s="59"/>
+      <c r="BY162" s="59"/>
+      <c r="BZ162" s="59"/>
+      <c r="CA162" s="59"/>
+      <c r="CB162" s="59"/>
+      <c r="CC162" s="59"/>
+      <c r="CD162" s="59"/>
+      <c r="CE162" s="59"/>
+      <c r="CF162" s="59"/>
+      <c r="CG162" s="59"/>
+      <c r="CH162" s="59"/>
+      <c r="CI162" s="59"/>
+      <c r="CJ162" s="59"/>
+      <c r="CK162" s="59"/>
+      <c r="CL162" s="59"/>
+      <c r="CM162" s="59"/>
+      <c r="CN162" s="59"/>
+      <c r="CO162" s="59"/>
+      <c r="CP162" s="59"/>
+      <c r="CQ162" s="59"/>
+      <c r="CR162" s="59"/>
+      <c r="CS162" s="59"/>
+      <c r="CT162" s="59"/>
+      <c r="CU162" s="59"/>
+      <c r="CV162" s="59"/>
+      <c r="CW162" s="59"/>
+      <c r="CX162" s="59"/>
+      <c r="CY162" s="59"/>
+      <c r="CZ162" s="59"/>
+      <c r="DA162" s="59"/>
+      <c r="DB162" s="59"/>
+      <c r="DC162" s="59"/>
+      <c r="DD162" s="59"/>
+      <c r="DE162" s="59"/>
+      <c r="DF162" s="59"/>
+      <c r="DG162" s="59"/>
+      <c r="DH162" s="59"/>
+      <c r="DI162" s="59"/>
+      <c r="DJ162" s="59"/>
+      <c r="DK162" s="59"/>
+      <c r="DL162" s="59"/>
+      <c r="DM162" s="59"/>
+      <c r="DN162" s="59"/>
+      <c r="DO162" s="59"/>
+      <c r="DP162" s="59"/>
+      <c r="DQ162" s="59"/>
+      <c r="DR162" s="59"/>
+      <c r="DS162" s="59"/>
+      <c r="DT162" s="59"/>
+      <c r="DU162" s="59"/>
+      <c r="DV162" s="59"/>
+      <c r="DW162" s="59"/>
+      <c r="DX162" s="59"/>
+      <c r="DY162" s="59"/>
+      <c r="DZ162" s="59"/>
+      <c r="EA162" s="59"/>
+      <c r="EB162" s="59"/>
+      <c r="EC162" s="59"/>
+      <c r="ED162" s="59"/>
+      <c r="EE162" s="59"/>
+      <c r="EF162" s="59"/>
+      <c r="EG162" s="59"/>
+      <c r="EH162" s="59"/>
+      <c r="EI162" s="59"/>
+      <c r="EJ162" s="59"/>
+      <c r="EK162" s="59"/>
+      <c r="EL162" s="59"/>
+      <c r="EM162" s="59"/>
+      <c r="EN162" s="59"/>
+      <c r="EO162" s="59"/>
+      <c r="EP162" s="59"/>
+      <c r="EQ162" s="59"/>
+      <c r="ER162" s="59"/>
+      <c r="ES162" s="59"/>
+      <c r="ET162" s="59"/>
+      <c r="EU162" s="59"/>
+      <c r="EV162" s="59"/>
+      <c r="EW162" s="59"/>
+      <c r="EX162" s="59"/>
+      <c r="EY162" s="59"/>
+      <c r="EZ162" s="59"/>
+      <c r="FA162" s="59"/>
+      <c r="FB162" s="59"/>
+      <c r="FC162" s="59"/>
+      <c r="FD162" s="59"/>
+      <c r="FE162" s="59"/>
+      <c r="FF162" s="59"/>
+      <c r="FG162" s="59"/>
+      <c r="FH162" s="59"/>
+      <c r="FI162" s="59"/>
+      <c r="FJ162" s="59"/>
+      <c r="FK162" s="59"/>
+      <c r="FL162" s="59"/>
+      <c r="FM162" s="59"/>
+      <c r="FN162" s="59"/>
+      <c r="FO162" s="60"/>
+    </row>
+    <row r="163" s="5" customFormat="1" ht="57" customHeight="1" spans="1:171">
       <c r="A163" s="40">
         <v>5</v>
       </c>
-      <c r="B163" s="135" t="s">
+      <c r="B163" s="144" t="s">
         <v>226</v>
       </c>
-      <c r="C163" s="135"/>
-      <c r="D163" s="135"/>
-      <c r="E163" s="135"/>
-      <c r="F163" s="135"/>
-      <c r="G163" s="135"/>
-      <c r="H163" s="135"/>
-      <c r="I163" s="135"/>
-      <c r="J163" s="118"/>
-      <c r="K163" s="119"/>
-      <c r="L163" s="119"/>
-    </row>
-    <row r="164" s="5" customFormat="1" ht="31.5" customHeight="1" spans="1:12">
+      <c r="C163" s="144"/>
+      <c r="D163" s="144"/>
+      <c r="E163" s="144"/>
+      <c r="F163" s="144"/>
+      <c r="G163" s="144"/>
+      <c r="H163" s="144"/>
+      <c r="I163" s="145"/>
+      <c r="J163" s="125"/>
+      <c r="K163" s="125"/>
+      <c r="L163" s="125"/>
+      <c r="M163" s="59"/>
+      <c r="N163" s="59"/>
+      <c r="O163" s="59"/>
+      <c r="P163" s="59"/>
+      <c r="Q163" s="59"/>
+      <c r="R163" s="59"/>
+      <c r="S163" s="59"/>
+      <c r="T163" s="59"/>
+      <c r="U163" s="59"/>
+      <c r="V163" s="59"/>
+      <c r="W163" s="59"/>
+      <c r="X163" s="59"/>
+      <c r="Y163" s="59"/>
+      <c r="Z163" s="59"/>
+      <c r="AA163" s="59"/>
+      <c r="AB163" s="59"/>
+      <c r="AC163" s="59"/>
+      <c r="AD163" s="59"/>
+      <c r="AE163" s="59"/>
+      <c r="AF163" s="59"/>
+      <c r="AG163" s="59"/>
+      <c r="AH163" s="59"/>
+      <c r="AI163" s="59"/>
+      <c r="AJ163" s="59"/>
+      <c r="AK163" s="59"/>
+      <c r="AL163" s="59"/>
+      <c r="AM163" s="59"/>
+      <c r="AN163" s="59"/>
+      <c r="AO163" s="59"/>
+      <c r="AP163" s="59"/>
+      <c r="AQ163" s="59"/>
+      <c r="AR163" s="59"/>
+      <c r="AS163" s="59"/>
+      <c r="AT163" s="59"/>
+      <c r="AU163" s="59"/>
+      <c r="AV163" s="59"/>
+      <c r="AW163" s="59"/>
+      <c r="AX163" s="59"/>
+      <c r="AY163" s="59"/>
+      <c r="AZ163" s="59"/>
+      <c r="BA163" s="59"/>
+      <c r="BB163" s="59"/>
+      <c r="BC163" s="59"/>
+      <c r="BD163" s="59"/>
+      <c r="BE163" s="59"/>
+      <c r="BF163" s="59"/>
+      <c r="BG163" s="59"/>
+      <c r="BH163" s="59"/>
+      <c r="BI163" s="59"/>
+      <c r="BJ163" s="59"/>
+      <c r="BK163" s="59"/>
+      <c r="BL163" s="59"/>
+      <c r="BM163" s="59"/>
+      <c r="BN163" s="59"/>
+      <c r="BO163" s="59"/>
+      <c r="BP163" s="59"/>
+      <c r="BQ163" s="59"/>
+      <c r="BR163" s="59"/>
+      <c r="BS163" s="59"/>
+      <c r="BT163" s="59"/>
+      <c r="BU163" s="59"/>
+      <c r="BV163" s="59"/>
+      <c r="BW163" s="59"/>
+      <c r="BX163" s="59"/>
+      <c r="BY163" s="59"/>
+      <c r="BZ163" s="59"/>
+      <c r="CA163" s="59"/>
+      <c r="CB163" s="59"/>
+      <c r="CC163" s="59"/>
+      <c r="CD163" s="59"/>
+      <c r="CE163" s="59"/>
+      <c r="CF163" s="59"/>
+      <c r="CG163" s="59"/>
+      <c r="CH163" s="59"/>
+      <c r="CI163" s="59"/>
+      <c r="CJ163" s="59"/>
+      <c r="CK163" s="59"/>
+      <c r="CL163" s="59"/>
+      <c r="CM163" s="59"/>
+      <c r="CN163" s="59"/>
+      <c r="CO163" s="59"/>
+      <c r="CP163" s="59"/>
+      <c r="CQ163" s="59"/>
+      <c r="CR163" s="59"/>
+      <c r="CS163" s="59"/>
+      <c r="CT163" s="59"/>
+      <c r="CU163" s="59"/>
+      <c r="CV163" s="59"/>
+      <c r="CW163" s="59"/>
+      <c r="CX163" s="59"/>
+      <c r="CY163" s="59"/>
+      <c r="CZ163" s="59"/>
+      <c r="DA163" s="59"/>
+      <c r="DB163" s="59"/>
+      <c r="DC163" s="59"/>
+      <c r="DD163" s="59"/>
+      <c r="DE163" s="59"/>
+      <c r="DF163" s="59"/>
+      <c r="DG163" s="59"/>
+      <c r="DH163" s="59"/>
+      <c r="DI163" s="59"/>
+      <c r="DJ163" s="59"/>
+      <c r="DK163" s="59"/>
+      <c r="DL163" s="59"/>
+      <c r="DM163" s="59"/>
+      <c r="DN163" s="59"/>
+      <c r="DO163" s="59"/>
+      <c r="DP163" s="59"/>
+      <c r="DQ163" s="59"/>
+      <c r="DR163" s="59"/>
+      <c r="DS163" s="59"/>
+      <c r="DT163" s="59"/>
+      <c r="DU163" s="59"/>
+      <c r="DV163" s="59"/>
+      <c r="DW163" s="59"/>
+      <c r="DX163" s="59"/>
+      <c r="DY163" s="59"/>
+      <c r="DZ163" s="59"/>
+      <c r="EA163" s="59"/>
+      <c r="EB163" s="59"/>
+      <c r="EC163" s="59"/>
+      <c r="ED163" s="59"/>
+      <c r="EE163" s="59"/>
+      <c r="EF163" s="59"/>
+      <c r="EG163" s="59"/>
+      <c r="EH163" s="59"/>
+      <c r="EI163" s="59"/>
+      <c r="EJ163" s="59"/>
+      <c r="EK163" s="59"/>
+      <c r="EL163" s="59"/>
+      <c r="EM163" s="59"/>
+      <c r="EN163" s="59"/>
+      <c r="EO163" s="59"/>
+      <c r="EP163" s="59"/>
+      <c r="EQ163" s="59"/>
+      <c r="ER163" s="59"/>
+      <c r="ES163" s="59"/>
+      <c r="ET163" s="59"/>
+      <c r="EU163" s="59"/>
+      <c r="EV163" s="59"/>
+      <c r="EW163" s="59"/>
+      <c r="EX163" s="59"/>
+      <c r="EY163" s="59"/>
+      <c r="EZ163" s="59"/>
+      <c r="FA163" s="59"/>
+      <c r="FB163" s="59"/>
+      <c r="FC163" s="59"/>
+      <c r="FD163" s="59"/>
+      <c r="FE163" s="59"/>
+      <c r="FF163" s="59"/>
+      <c r="FG163" s="59"/>
+      <c r="FH163" s="59"/>
+      <c r="FI163" s="59"/>
+      <c r="FJ163" s="59"/>
+      <c r="FK163" s="59"/>
+      <c r="FL163" s="59"/>
+      <c r="FM163" s="59"/>
+      <c r="FN163" s="59"/>
+      <c r="FO163" s="60"/>
+    </row>
+    <row r="164" s="5" customFormat="1" ht="31.5" customHeight="1" spans="1:171">
       <c r="A164" s="40">
         <v>6</v>
       </c>
@@ -7736,80 +8900,874 @@
       <c r="F164" s="43"/>
       <c r="G164" s="43"/>
       <c r="H164" s="43"/>
-      <c r="I164" s="43"/>
-      <c r="J164" s="118"/>
-      <c r="K164" s="119"/>
-      <c r="L164" s="119"/>
-    </row>
-    <row r="165" s="5" customFormat="1" ht="16.5" customHeight="1" spans="1:12">
+      <c r="I164" s="133"/>
+      <c r="J164" s="125"/>
+      <c r="K164" s="125"/>
+      <c r="L164" s="125"/>
+      <c r="M164" s="59"/>
+      <c r="N164" s="59"/>
+      <c r="O164" s="59"/>
+      <c r="P164" s="59"/>
+      <c r="Q164" s="59"/>
+      <c r="R164" s="59"/>
+      <c r="S164" s="59"/>
+      <c r="T164" s="59"/>
+      <c r="U164" s="59"/>
+      <c r="V164" s="59"/>
+      <c r="W164" s="59"/>
+      <c r="X164" s="59"/>
+      <c r="Y164" s="59"/>
+      <c r="Z164" s="59"/>
+      <c r="AA164" s="59"/>
+      <c r="AB164" s="59"/>
+      <c r="AC164" s="59"/>
+      <c r="AD164" s="59"/>
+      <c r="AE164" s="59"/>
+      <c r="AF164" s="59"/>
+      <c r="AG164" s="59"/>
+      <c r="AH164" s="59"/>
+      <c r="AI164" s="59"/>
+      <c r="AJ164" s="59"/>
+      <c r="AK164" s="59"/>
+      <c r="AL164" s="59"/>
+      <c r="AM164" s="59"/>
+      <c r="AN164" s="59"/>
+      <c r="AO164" s="59"/>
+      <c r="AP164" s="59"/>
+      <c r="AQ164" s="59"/>
+      <c r="AR164" s="59"/>
+      <c r="AS164" s="59"/>
+      <c r="AT164" s="59"/>
+      <c r="AU164" s="59"/>
+      <c r="AV164" s="59"/>
+      <c r="AW164" s="59"/>
+      <c r="AX164" s="59"/>
+      <c r="AY164" s="59"/>
+      <c r="AZ164" s="59"/>
+      <c r="BA164" s="59"/>
+      <c r="BB164" s="59"/>
+      <c r="BC164" s="59"/>
+      <c r="BD164" s="59"/>
+      <c r="BE164" s="59"/>
+      <c r="BF164" s="59"/>
+      <c r="BG164" s="59"/>
+      <c r="BH164" s="59"/>
+      <c r="BI164" s="59"/>
+      <c r="BJ164" s="59"/>
+      <c r="BK164" s="59"/>
+      <c r="BL164" s="59"/>
+      <c r="BM164" s="59"/>
+      <c r="BN164" s="59"/>
+      <c r="BO164" s="59"/>
+      <c r="BP164" s="59"/>
+      <c r="BQ164" s="59"/>
+      <c r="BR164" s="59"/>
+      <c r="BS164" s="59"/>
+      <c r="BT164" s="59"/>
+      <c r="BU164" s="59"/>
+      <c r="BV164" s="59"/>
+      <c r="BW164" s="59"/>
+      <c r="BX164" s="59"/>
+      <c r="BY164" s="59"/>
+      <c r="BZ164" s="59"/>
+      <c r="CA164" s="59"/>
+      <c r="CB164" s="59"/>
+      <c r="CC164" s="59"/>
+      <c r="CD164" s="59"/>
+      <c r="CE164" s="59"/>
+      <c r="CF164" s="59"/>
+      <c r="CG164" s="59"/>
+      <c r="CH164" s="59"/>
+      <c r="CI164" s="59"/>
+      <c r="CJ164" s="59"/>
+      <c r="CK164" s="59"/>
+      <c r="CL164" s="59"/>
+      <c r="CM164" s="59"/>
+      <c r="CN164" s="59"/>
+      <c r="CO164" s="59"/>
+      <c r="CP164" s="59"/>
+      <c r="CQ164" s="59"/>
+      <c r="CR164" s="59"/>
+      <c r="CS164" s="59"/>
+      <c r="CT164" s="59"/>
+      <c r="CU164" s="59"/>
+      <c r="CV164" s="59"/>
+      <c r="CW164" s="59"/>
+      <c r="CX164" s="59"/>
+      <c r="CY164" s="59"/>
+      <c r="CZ164" s="59"/>
+      <c r="DA164" s="59"/>
+      <c r="DB164" s="59"/>
+      <c r="DC164" s="59"/>
+      <c r="DD164" s="59"/>
+      <c r="DE164" s="59"/>
+      <c r="DF164" s="59"/>
+      <c r="DG164" s="59"/>
+      <c r="DH164" s="59"/>
+      <c r="DI164" s="59"/>
+      <c r="DJ164" s="59"/>
+      <c r="DK164" s="59"/>
+      <c r="DL164" s="59"/>
+      <c r="DM164" s="59"/>
+      <c r="DN164" s="59"/>
+      <c r="DO164" s="59"/>
+      <c r="DP164" s="59"/>
+      <c r="DQ164" s="59"/>
+      <c r="DR164" s="59"/>
+      <c r="DS164" s="59"/>
+      <c r="DT164" s="59"/>
+      <c r="DU164" s="59"/>
+      <c r="DV164" s="59"/>
+      <c r="DW164" s="59"/>
+      <c r="DX164" s="59"/>
+      <c r="DY164" s="59"/>
+      <c r="DZ164" s="59"/>
+      <c r="EA164" s="59"/>
+      <c r="EB164" s="59"/>
+      <c r="EC164" s="59"/>
+      <c r="ED164" s="59"/>
+      <c r="EE164" s="59"/>
+      <c r="EF164" s="59"/>
+      <c r="EG164" s="59"/>
+      <c r="EH164" s="59"/>
+      <c r="EI164" s="59"/>
+      <c r="EJ164" s="59"/>
+      <c r="EK164" s="59"/>
+      <c r="EL164" s="59"/>
+      <c r="EM164" s="59"/>
+      <c r="EN164" s="59"/>
+      <c r="EO164" s="59"/>
+      <c r="EP164" s="59"/>
+      <c r="EQ164" s="59"/>
+      <c r="ER164" s="59"/>
+      <c r="ES164" s="59"/>
+      <c r="ET164" s="59"/>
+      <c r="EU164" s="59"/>
+      <c r="EV164" s="59"/>
+      <c r="EW164" s="59"/>
+      <c r="EX164" s="59"/>
+      <c r="EY164" s="59"/>
+      <c r="EZ164" s="59"/>
+      <c r="FA164" s="59"/>
+      <c r="FB164" s="59"/>
+      <c r="FC164" s="59"/>
+      <c r="FD164" s="59"/>
+      <c r="FE164" s="59"/>
+      <c r="FF164" s="59"/>
+      <c r="FG164" s="59"/>
+      <c r="FH164" s="59"/>
+      <c r="FI164" s="59"/>
+      <c r="FJ164" s="59"/>
+      <c r="FK164" s="59"/>
+      <c r="FL164" s="59"/>
+      <c r="FM164" s="59"/>
+      <c r="FN164" s="59"/>
+      <c r="FO164" s="60"/>
+    </row>
+    <row r="165" s="5" customFormat="1" ht="16.5" customHeight="1" spans="1:171">
       <c r="A165" s="40">
         <v>7</v>
       </c>
-      <c r="B165" s="135" t="s">
+      <c r="B165" s="144" t="s">
         <v>228</v>
       </c>
-      <c r="C165" s="135"/>
-      <c r="D165" s="135"/>
-      <c r="E165" s="135"/>
-      <c r="F165" s="135"/>
-      <c r="G165" s="135"/>
-      <c r="H165" s="135"/>
-      <c r="I165" s="135"/>
-      <c r="J165" s="118"/>
-      <c r="K165" s="119"/>
-      <c r="L165" s="119"/>
-    </row>
-    <row r="166" s="5" customFormat="1" ht="16" customHeight="1" spans="1:12">
+      <c r="C165" s="144"/>
+      <c r="D165" s="144"/>
+      <c r="E165" s="144"/>
+      <c r="F165" s="144"/>
+      <c r="G165" s="144"/>
+      <c r="H165" s="144"/>
+      <c r="I165" s="145"/>
+      <c r="J165" s="125"/>
+      <c r="K165" s="125"/>
+      <c r="L165" s="125"/>
+      <c r="M165" s="59"/>
+      <c r="N165" s="59"/>
+      <c r="O165" s="59"/>
+      <c r="P165" s="59"/>
+      <c r="Q165" s="59"/>
+      <c r="R165" s="59"/>
+      <c r="S165" s="59"/>
+      <c r="T165" s="59"/>
+      <c r="U165" s="59"/>
+      <c r="V165" s="59"/>
+      <c r="W165" s="59"/>
+      <c r="X165" s="59"/>
+      <c r="Y165" s="59"/>
+      <c r="Z165" s="59"/>
+      <c r="AA165" s="59"/>
+      <c r="AB165" s="59"/>
+      <c r="AC165" s="59"/>
+      <c r="AD165" s="59"/>
+      <c r="AE165" s="59"/>
+      <c r="AF165" s="59"/>
+      <c r="AG165" s="59"/>
+      <c r="AH165" s="59"/>
+      <c r="AI165" s="59"/>
+      <c r="AJ165" s="59"/>
+      <c r="AK165" s="59"/>
+      <c r="AL165" s="59"/>
+      <c r="AM165" s="59"/>
+      <c r="AN165" s="59"/>
+      <c r="AO165" s="59"/>
+      <c r="AP165" s="59"/>
+      <c r="AQ165" s="59"/>
+      <c r="AR165" s="59"/>
+      <c r="AS165" s="59"/>
+      <c r="AT165" s="59"/>
+      <c r="AU165" s="59"/>
+      <c r="AV165" s="59"/>
+      <c r="AW165" s="59"/>
+      <c r="AX165" s="59"/>
+      <c r="AY165" s="59"/>
+      <c r="AZ165" s="59"/>
+      <c r="BA165" s="59"/>
+      <c r="BB165" s="59"/>
+      <c r="BC165" s="59"/>
+      <c r="BD165" s="59"/>
+      <c r="BE165" s="59"/>
+      <c r="BF165" s="59"/>
+      <c r="BG165" s="59"/>
+      <c r="BH165" s="59"/>
+      <c r="BI165" s="59"/>
+      <c r="BJ165" s="59"/>
+      <c r="BK165" s="59"/>
+      <c r="BL165" s="59"/>
+      <c r="BM165" s="59"/>
+      <c r="BN165" s="59"/>
+      <c r="BO165" s="59"/>
+      <c r="BP165" s="59"/>
+      <c r="BQ165" s="59"/>
+      <c r="BR165" s="59"/>
+      <c r="BS165" s="59"/>
+      <c r="BT165" s="59"/>
+      <c r="BU165" s="59"/>
+      <c r="BV165" s="59"/>
+      <c r="BW165" s="59"/>
+      <c r="BX165" s="59"/>
+      <c r="BY165" s="59"/>
+      <c r="BZ165" s="59"/>
+      <c r="CA165" s="59"/>
+      <c r="CB165" s="59"/>
+      <c r="CC165" s="59"/>
+      <c r="CD165" s="59"/>
+      <c r="CE165" s="59"/>
+      <c r="CF165" s="59"/>
+      <c r="CG165" s="59"/>
+      <c r="CH165" s="59"/>
+      <c r="CI165" s="59"/>
+      <c r="CJ165" s="59"/>
+      <c r="CK165" s="59"/>
+      <c r="CL165" s="59"/>
+      <c r="CM165" s="59"/>
+      <c r="CN165" s="59"/>
+      <c r="CO165" s="59"/>
+      <c r="CP165" s="59"/>
+      <c r="CQ165" s="59"/>
+      <c r="CR165" s="59"/>
+      <c r="CS165" s="59"/>
+      <c r="CT165" s="59"/>
+      <c r="CU165" s="59"/>
+      <c r="CV165" s="59"/>
+      <c r="CW165" s="59"/>
+      <c r="CX165" s="59"/>
+      <c r="CY165" s="59"/>
+      <c r="CZ165" s="59"/>
+      <c r="DA165" s="59"/>
+      <c r="DB165" s="59"/>
+      <c r="DC165" s="59"/>
+      <c r="DD165" s="59"/>
+      <c r="DE165" s="59"/>
+      <c r="DF165" s="59"/>
+      <c r="DG165" s="59"/>
+      <c r="DH165" s="59"/>
+      <c r="DI165" s="59"/>
+      <c r="DJ165" s="59"/>
+      <c r="DK165" s="59"/>
+      <c r="DL165" s="59"/>
+      <c r="DM165" s="59"/>
+      <c r="DN165" s="59"/>
+      <c r="DO165" s="59"/>
+      <c r="DP165" s="59"/>
+      <c r="DQ165" s="59"/>
+      <c r="DR165" s="59"/>
+      <c r="DS165" s="59"/>
+      <c r="DT165" s="59"/>
+      <c r="DU165" s="59"/>
+      <c r="DV165" s="59"/>
+      <c r="DW165" s="59"/>
+      <c r="DX165" s="59"/>
+      <c r="DY165" s="59"/>
+      <c r="DZ165" s="59"/>
+      <c r="EA165" s="59"/>
+      <c r="EB165" s="59"/>
+      <c r="EC165" s="59"/>
+      <c r="ED165" s="59"/>
+      <c r="EE165" s="59"/>
+      <c r="EF165" s="59"/>
+      <c r="EG165" s="59"/>
+      <c r="EH165" s="59"/>
+      <c r="EI165" s="59"/>
+      <c r="EJ165" s="59"/>
+      <c r="EK165" s="59"/>
+      <c r="EL165" s="59"/>
+      <c r="EM165" s="59"/>
+      <c r="EN165" s="59"/>
+      <c r="EO165" s="59"/>
+      <c r="EP165" s="59"/>
+      <c r="EQ165" s="59"/>
+      <c r="ER165" s="59"/>
+      <c r="ES165" s="59"/>
+      <c r="ET165" s="59"/>
+      <c r="EU165" s="59"/>
+      <c r="EV165" s="59"/>
+      <c r="EW165" s="59"/>
+      <c r="EX165" s="59"/>
+      <c r="EY165" s="59"/>
+      <c r="EZ165" s="59"/>
+      <c r="FA165" s="59"/>
+      <c r="FB165" s="59"/>
+      <c r="FC165" s="59"/>
+      <c r="FD165" s="59"/>
+      <c r="FE165" s="59"/>
+      <c r="FF165" s="59"/>
+      <c r="FG165" s="59"/>
+      <c r="FH165" s="59"/>
+      <c r="FI165" s="59"/>
+      <c r="FJ165" s="59"/>
+      <c r="FK165" s="59"/>
+      <c r="FL165" s="59"/>
+      <c r="FM165" s="59"/>
+      <c r="FN165" s="59"/>
+      <c r="FO165" s="60"/>
+    </row>
+    <row r="166" s="5" customFormat="1" ht="16" customHeight="1" spans="1:171">
       <c r="A166" s="40">
         <v>8</v>
       </c>
-      <c r="B166" s="135" t="s">
+      <c r="B166" s="144" t="s">
         <v>229</v>
       </c>
-      <c r="C166" s="135"/>
-      <c r="D166" s="135"/>
-      <c r="E166" s="135"/>
-      <c r="F166" s="135"/>
-      <c r="G166" s="135"/>
-      <c r="H166" s="135"/>
-      <c r="I166" s="135"/>
-      <c r="J166" s="118"/>
-      <c r="K166" s="119"/>
-      <c r="L166" s="119"/>
-    </row>
-    <row r="167" s="5" customFormat="1" ht="16" customHeight="1" spans="1:12">
+      <c r="C166" s="144"/>
+      <c r="D166" s="144"/>
+      <c r="E166" s="144"/>
+      <c r="F166" s="144"/>
+      <c r="G166" s="144"/>
+      <c r="H166" s="144"/>
+      <c r="I166" s="145"/>
+      <c r="J166" s="125"/>
+      <c r="K166" s="125"/>
+      <c r="L166" s="125"/>
+      <c r="M166" s="59"/>
+      <c r="N166" s="59"/>
+      <c r="O166" s="59"/>
+      <c r="P166" s="59"/>
+      <c r="Q166" s="59"/>
+      <c r="R166" s="59"/>
+      <c r="S166" s="59"/>
+      <c r="T166" s="59"/>
+      <c r="U166" s="59"/>
+      <c r="V166" s="59"/>
+      <c r="W166" s="59"/>
+      <c r="X166" s="59"/>
+      <c r="Y166" s="59"/>
+      <c r="Z166" s="59"/>
+      <c r="AA166" s="59"/>
+      <c r="AB166" s="59"/>
+      <c r="AC166" s="59"/>
+      <c r="AD166" s="59"/>
+      <c r="AE166" s="59"/>
+      <c r="AF166" s="59"/>
+      <c r="AG166" s="59"/>
+      <c r="AH166" s="59"/>
+      <c r="AI166" s="59"/>
+      <c r="AJ166" s="59"/>
+      <c r="AK166" s="59"/>
+      <c r="AL166" s="59"/>
+      <c r="AM166" s="59"/>
+      <c r="AN166" s="59"/>
+      <c r="AO166" s="59"/>
+      <c r="AP166" s="59"/>
+      <c r="AQ166" s="59"/>
+      <c r="AR166" s="59"/>
+      <c r="AS166" s="59"/>
+      <c r="AT166" s="59"/>
+      <c r="AU166" s="59"/>
+      <c r="AV166" s="59"/>
+      <c r="AW166" s="59"/>
+      <c r="AX166" s="59"/>
+      <c r="AY166" s="59"/>
+      <c r="AZ166" s="59"/>
+      <c r="BA166" s="59"/>
+      <c r="BB166" s="59"/>
+      <c r="BC166" s="59"/>
+      <c r="BD166" s="59"/>
+      <c r="BE166" s="59"/>
+      <c r="BF166" s="59"/>
+      <c r="BG166" s="59"/>
+      <c r="BH166" s="59"/>
+      <c r="BI166" s="59"/>
+      <c r="BJ166" s="59"/>
+      <c r="BK166" s="59"/>
+      <c r="BL166" s="59"/>
+      <c r="BM166" s="59"/>
+      <c r="BN166" s="59"/>
+      <c r="BO166" s="59"/>
+      <c r="BP166" s="59"/>
+      <c r="BQ166" s="59"/>
+      <c r="BR166" s="59"/>
+      <c r="BS166" s="59"/>
+      <c r="BT166" s="59"/>
+      <c r="BU166" s="59"/>
+      <c r="BV166" s="59"/>
+      <c r="BW166" s="59"/>
+      <c r="BX166" s="59"/>
+      <c r="BY166" s="59"/>
+      <c r="BZ166" s="59"/>
+      <c r="CA166" s="59"/>
+      <c r="CB166" s="59"/>
+      <c r="CC166" s="59"/>
+      <c r="CD166" s="59"/>
+      <c r="CE166" s="59"/>
+      <c r="CF166" s="59"/>
+      <c r="CG166" s="59"/>
+      <c r="CH166" s="59"/>
+      <c r="CI166" s="59"/>
+      <c r="CJ166" s="59"/>
+      <c r="CK166" s="59"/>
+      <c r="CL166" s="59"/>
+      <c r="CM166" s="59"/>
+      <c r="CN166" s="59"/>
+      <c r="CO166" s="59"/>
+      <c r="CP166" s="59"/>
+      <c r="CQ166" s="59"/>
+      <c r="CR166" s="59"/>
+      <c r="CS166" s="59"/>
+      <c r="CT166" s="59"/>
+      <c r="CU166" s="59"/>
+      <c r="CV166" s="59"/>
+      <c r="CW166" s="59"/>
+      <c r="CX166" s="59"/>
+      <c r="CY166" s="59"/>
+      <c r="CZ166" s="59"/>
+      <c r="DA166" s="59"/>
+      <c r="DB166" s="59"/>
+      <c r="DC166" s="59"/>
+      <c r="DD166" s="59"/>
+      <c r="DE166" s="59"/>
+      <c r="DF166" s="59"/>
+      <c r="DG166" s="59"/>
+      <c r="DH166" s="59"/>
+      <c r="DI166" s="59"/>
+      <c r="DJ166" s="59"/>
+      <c r="DK166" s="59"/>
+      <c r="DL166" s="59"/>
+      <c r="DM166" s="59"/>
+      <c r="DN166" s="59"/>
+      <c r="DO166" s="59"/>
+      <c r="DP166" s="59"/>
+      <c r="DQ166" s="59"/>
+      <c r="DR166" s="59"/>
+      <c r="DS166" s="59"/>
+      <c r="DT166" s="59"/>
+      <c r="DU166" s="59"/>
+      <c r="DV166" s="59"/>
+      <c r="DW166" s="59"/>
+      <c r="DX166" s="59"/>
+      <c r="DY166" s="59"/>
+      <c r="DZ166" s="59"/>
+      <c r="EA166" s="59"/>
+      <c r="EB166" s="59"/>
+      <c r="EC166" s="59"/>
+      <c r="ED166" s="59"/>
+      <c r="EE166" s="59"/>
+      <c r="EF166" s="59"/>
+      <c r="EG166" s="59"/>
+      <c r="EH166" s="59"/>
+      <c r="EI166" s="59"/>
+      <c r="EJ166" s="59"/>
+      <c r="EK166" s="59"/>
+      <c r="EL166" s="59"/>
+      <c r="EM166" s="59"/>
+      <c r="EN166" s="59"/>
+      <c r="EO166" s="59"/>
+      <c r="EP166" s="59"/>
+      <c r="EQ166" s="59"/>
+      <c r="ER166" s="59"/>
+      <c r="ES166" s="59"/>
+      <c r="ET166" s="59"/>
+      <c r="EU166" s="59"/>
+      <c r="EV166" s="59"/>
+      <c r="EW166" s="59"/>
+      <c r="EX166" s="59"/>
+      <c r="EY166" s="59"/>
+      <c r="EZ166" s="59"/>
+      <c r="FA166" s="59"/>
+      <c r="FB166" s="59"/>
+      <c r="FC166" s="59"/>
+      <c r="FD166" s="59"/>
+      <c r="FE166" s="59"/>
+      <c r="FF166" s="59"/>
+      <c r="FG166" s="59"/>
+      <c r="FH166" s="59"/>
+      <c r="FI166" s="59"/>
+      <c r="FJ166" s="59"/>
+      <c r="FK166" s="59"/>
+      <c r="FL166" s="59"/>
+      <c r="FM166" s="59"/>
+      <c r="FN166" s="59"/>
+      <c r="FO166" s="60"/>
+    </row>
+    <row r="167" s="5" customFormat="1" ht="16" customHeight="1" spans="1:171">
       <c r="A167" s="40">
         <v>9</v>
       </c>
-      <c r="B167" s="135" t="s">
+      <c r="B167" s="144" t="s">
         <v>230</v>
       </c>
-      <c r="C167" s="135"/>
-      <c r="D167" s="135"/>
-      <c r="E167" s="135"/>
-      <c r="F167" s="135"/>
-      <c r="G167" s="135"/>
-      <c r="H167" s="135"/>
-      <c r="I167" s="135"/>
-      <c r="J167" s="118"/>
-      <c r="K167" s="119"/>
-      <c r="L167" s="119"/>
-    </row>
-    <row r="168" s="18" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A168" s="136"/>
-      <c r="B168" s="137" t="s">
+      <c r="C167" s="144"/>
+      <c r="D167" s="144"/>
+      <c r="E167" s="144"/>
+      <c r="F167" s="144"/>
+      <c r="G167" s="144"/>
+      <c r="H167" s="144"/>
+      <c r="I167" s="145"/>
+      <c r="J167" s="125"/>
+      <c r="K167" s="125"/>
+      <c r="L167" s="125"/>
+      <c r="M167" s="59"/>
+      <c r="N167" s="59"/>
+      <c r="O167" s="59"/>
+      <c r="P167" s="59"/>
+      <c r="Q167" s="59"/>
+      <c r="R167" s="59"/>
+      <c r="S167" s="59"/>
+      <c r="T167" s="59"/>
+      <c r="U167" s="59"/>
+      <c r="V167" s="59"/>
+      <c r="W167" s="59"/>
+      <c r="X167" s="59"/>
+      <c r="Y167" s="59"/>
+      <c r="Z167" s="59"/>
+      <c r="AA167" s="59"/>
+      <c r="AB167" s="59"/>
+      <c r="AC167" s="59"/>
+      <c r="AD167" s="59"/>
+      <c r="AE167" s="59"/>
+      <c r="AF167" s="59"/>
+      <c r="AG167" s="59"/>
+      <c r="AH167" s="59"/>
+      <c r="AI167" s="59"/>
+      <c r="AJ167" s="59"/>
+      <c r="AK167" s="59"/>
+      <c r="AL167" s="59"/>
+      <c r="AM167" s="59"/>
+      <c r="AN167" s="59"/>
+      <c r="AO167" s="59"/>
+      <c r="AP167" s="59"/>
+      <c r="AQ167" s="59"/>
+      <c r="AR167" s="59"/>
+      <c r="AS167" s="59"/>
+      <c r="AT167" s="59"/>
+      <c r="AU167" s="59"/>
+      <c r="AV167" s="59"/>
+      <c r="AW167" s="59"/>
+      <c r="AX167" s="59"/>
+      <c r="AY167" s="59"/>
+      <c r="AZ167" s="59"/>
+      <c r="BA167" s="59"/>
+      <c r="BB167" s="59"/>
+      <c r="BC167" s="59"/>
+      <c r="BD167" s="59"/>
+      <c r="BE167" s="59"/>
+      <c r="BF167" s="59"/>
+      <c r="BG167" s="59"/>
+      <c r="BH167" s="59"/>
+      <c r="BI167" s="59"/>
+      <c r="BJ167" s="59"/>
+      <c r="BK167" s="59"/>
+      <c r="BL167" s="59"/>
+      <c r="BM167" s="59"/>
+      <c r="BN167" s="59"/>
+      <c r="BO167" s="59"/>
+      <c r="BP167" s="59"/>
+      <c r="BQ167" s="59"/>
+      <c r="BR167" s="59"/>
+      <c r="BS167" s="59"/>
+      <c r="BT167" s="59"/>
+      <c r="BU167" s="59"/>
+      <c r="BV167" s="59"/>
+      <c r="BW167" s="59"/>
+      <c r="BX167" s="59"/>
+      <c r="BY167" s="59"/>
+      <c r="BZ167" s="59"/>
+      <c r="CA167" s="59"/>
+      <c r="CB167" s="59"/>
+      <c r="CC167" s="59"/>
+      <c r="CD167" s="59"/>
+      <c r="CE167" s="59"/>
+      <c r="CF167" s="59"/>
+      <c r="CG167" s="59"/>
+      <c r="CH167" s="59"/>
+      <c r="CI167" s="59"/>
+      <c r="CJ167" s="59"/>
+      <c r="CK167" s="59"/>
+      <c r="CL167" s="59"/>
+      <c r="CM167" s="59"/>
+      <c r="CN167" s="59"/>
+      <c r="CO167" s="59"/>
+      <c r="CP167" s="59"/>
+      <c r="CQ167" s="59"/>
+      <c r="CR167" s="59"/>
+      <c r="CS167" s="59"/>
+      <c r="CT167" s="59"/>
+      <c r="CU167" s="59"/>
+      <c r="CV167" s="59"/>
+      <c r="CW167" s="59"/>
+      <c r="CX167" s="59"/>
+      <c r="CY167" s="59"/>
+      <c r="CZ167" s="59"/>
+      <c r="DA167" s="59"/>
+      <c r="DB167" s="59"/>
+      <c r="DC167" s="59"/>
+      <c r="DD167" s="59"/>
+      <c r="DE167" s="59"/>
+      <c r="DF167" s="59"/>
+      <c r="DG167" s="59"/>
+      <c r="DH167" s="59"/>
+      <c r="DI167" s="59"/>
+      <c r="DJ167" s="59"/>
+      <c r="DK167" s="59"/>
+      <c r="DL167" s="59"/>
+      <c r="DM167" s="59"/>
+      <c r="DN167" s="59"/>
+      <c r="DO167" s="59"/>
+      <c r="DP167" s="59"/>
+      <c r="DQ167" s="59"/>
+      <c r="DR167" s="59"/>
+      <c r="DS167" s="59"/>
+      <c r="DT167" s="59"/>
+      <c r="DU167" s="59"/>
+      <c r="DV167" s="59"/>
+      <c r="DW167" s="59"/>
+      <c r="DX167" s="59"/>
+      <c r="DY167" s="59"/>
+      <c r="DZ167" s="59"/>
+      <c r="EA167" s="59"/>
+      <c r="EB167" s="59"/>
+      <c r="EC167" s="59"/>
+      <c r="ED167" s="59"/>
+      <c r="EE167" s="59"/>
+      <c r="EF167" s="59"/>
+      <c r="EG167" s="59"/>
+      <c r="EH167" s="59"/>
+      <c r="EI167" s="59"/>
+      <c r="EJ167" s="59"/>
+      <c r="EK167" s="59"/>
+      <c r="EL167" s="59"/>
+      <c r="EM167" s="59"/>
+      <c r="EN167" s="59"/>
+      <c r="EO167" s="59"/>
+      <c r="EP167" s="59"/>
+      <c r="EQ167" s="59"/>
+      <c r="ER167" s="59"/>
+      <c r="ES167" s="59"/>
+      <c r="ET167" s="59"/>
+      <c r="EU167" s="59"/>
+      <c r="EV167" s="59"/>
+      <c r="EW167" s="59"/>
+      <c r="EX167" s="59"/>
+      <c r="EY167" s="59"/>
+      <c r="EZ167" s="59"/>
+      <c r="FA167" s="59"/>
+      <c r="FB167" s="59"/>
+      <c r="FC167" s="59"/>
+      <c r="FD167" s="59"/>
+      <c r="FE167" s="59"/>
+      <c r="FF167" s="59"/>
+      <c r="FG167" s="59"/>
+      <c r="FH167" s="59"/>
+      <c r="FI167" s="59"/>
+      <c r="FJ167" s="59"/>
+      <c r="FK167" s="59"/>
+      <c r="FL167" s="59"/>
+      <c r="FM167" s="59"/>
+      <c r="FN167" s="59"/>
+      <c r="FO167" s="60"/>
+    </row>
+    <row r="168" s="18" customFormat="1" ht="15.75" customHeight="1" spans="1:171">
+      <c r="A168" s="146"/>
+      <c r="B168" s="147" t="s">
         <v>231</v>
       </c>
-      <c r="C168" s="137"/>
-      <c r="D168" s="137"/>
-      <c r="E168" s="137"/>
-      <c r="F168" s="137"/>
-      <c r="G168" s="137"/>
-      <c r="H168" s="137"/>
-      <c r="I168" s="137"/>
-      <c r="J168" s="138"/>
-      <c r="K168" s="138"/>
-      <c r="L168" s="138"/>
+      <c r="C168" s="147"/>
+      <c r="D168" s="147"/>
+      <c r="E168" s="147"/>
+      <c r="F168" s="147"/>
+      <c r="G168" s="147"/>
+      <c r="H168" s="147"/>
+      <c r="I168" s="147"/>
+      <c r="J168" s="125"/>
+      <c r="K168" s="125"/>
+      <c r="L168" s="125"/>
+      <c r="M168" s="59"/>
+      <c r="N168" s="59"/>
+      <c r="O168" s="59"/>
+      <c r="P168" s="59"/>
+      <c r="Q168" s="59"/>
+      <c r="R168" s="59"/>
+      <c r="S168" s="59"/>
+      <c r="T168" s="59"/>
+      <c r="U168" s="59"/>
+      <c r="V168" s="59"/>
+      <c r="W168" s="59"/>
+      <c r="X168" s="59"/>
+      <c r="Y168" s="59"/>
+      <c r="Z168" s="59"/>
+      <c r="AA168" s="59"/>
+      <c r="AB168" s="59"/>
+      <c r="AC168" s="59"/>
+      <c r="AD168" s="59"/>
+      <c r="AE168" s="59"/>
+      <c r="AF168" s="59"/>
+      <c r="AG168" s="59"/>
+      <c r="AH168" s="59"/>
+      <c r="AI168" s="59"/>
+      <c r="AJ168" s="59"/>
+      <c r="AK168" s="59"/>
+      <c r="AL168" s="59"/>
+      <c r="AM168" s="59"/>
+      <c r="AN168" s="59"/>
+      <c r="AO168" s="59"/>
+      <c r="AP168" s="59"/>
+      <c r="AQ168" s="59"/>
+      <c r="AR168" s="59"/>
+      <c r="AS168" s="59"/>
+      <c r="AT168" s="59"/>
+      <c r="AU168" s="59"/>
+      <c r="AV168" s="59"/>
+      <c r="AW168" s="59"/>
+      <c r="AX168" s="59"/>
+      <c r="AY168" s="59"/>
+      <c r="AZ168" s="59"/>
+      <c r="BA168" s="59"/>
+      <c r="BB168" s="59"/>
+      <c r="BC168" s="59"/>
+      <c r="BD168" s="59"/>
+      <c r="BE168" s="59"/>
+      <c r="BF168" s="59"/>
+      <c r="BG168" s="59"/>
+      <c r="BH168" s="59"/>
+      <c r="BI168" s="59"/>
+      <c r="BJ168" s="59"/>
+      <c r="BK168" s="59"/>
+      <c r="BL168" s="59"/>
+      <c r="BM168" s="59"/>
+      <c r="BN168" s="59"/>
+      <c r="BO168" s="59"/>
+      <c r="BP168" s="59"/>
+      <c r="BQ168" s="59"/>
+      <c r="BR168" s="59"/>
+      <c r="BS168" s="59"/>
+      <c r="BT168" s="59"/>
+      <c r="BU168" s="59"/>
+      <c r="BV168" s="59"/>
+      <c r="BW168" s="59"/>
+      <c r="BX168" s="59"/>
+      <c r="BY168" s="59"/>
+      <c r="BZ168" s="59"/>
+      <c r="CA168" s="59"/>
+      <c r="CB168" s="59"/>
+      <c r="CC168" s="59"/>
+      <c r="CD168" s="59"/>
+      <c r="CE168" s="59"/>
+      <c r="CF168" s="59"/>
+      <c r="CG168" s="59"/>
+      <c r="CH168" s="59"/>
+      <c r="CI168" s="59"/>
+      <c r="CJ168" s="59"/>
+      <c r="CK168" s="59"/>
+      <c r="CL168" s="59"/>
+      <c r="CM168" s="59"/>
+      <c r="CN168" s="59"/>
+      <c r="CO168" s="59"/>
+      <c r="CP168" s="59"/>
+      <c r="CQ168" s="59"/>
+      <c r="CR168" s="59"/>
+      <c r="CS168" s="59"/>
+      <c r="CT168" s="59"/>
+      <c r="CU168" s="59"/>
+      <c r="CV168" s="59"/>
+      <c r="CW168" s="59"/>
+      <c r="CX168" s="59"/>
+      <c r="CY168" s="59"/>
+      <c r="CZ168" s="59"/>
+      <c r="DA168" s="59"/>
+      <c r="DB168" s="59"/>
+      <c r="DC168" s="59"/>
+      <c r="DD168" s="59"/>
+      <c r="DE168" s="59"/>
+      <c r="DF168" s="59"/>
+      <c r="DG168" s="59"/>
+      <c r="DH168" s="59"/>
+      <c r="DI168" s="59"/>
+      <c r="DJ168" s="59"/>
+      <c r="DK168" s="59"/>
+      <c r="DL168" s="59"/>
+      <c r="DM168" s="59"/>
+      <c r="DN168" s="59"/>
+      <c r="DO168" s="59"/>
+      <c r="DP168" s="59"/>
+      <c r="DQ168" s="59"/>
+      <c r="DR168" s="59"/>
+      <c r="DS168" s="59"/>
+      <c r="DT168" s="59"/>
+      <c r="DU168" s="59"/>
+      <c r="DV168" s="59"/>
+      <c r="DW168" s="59"/>
+      <c r="DX168" s="59"/>
+      <c r="DY168" s="59"/>
+      <c r="DZ168" s="59"/>
+      <c r="EA168" s="59"/>
+      <c r="EB168" s="59"/>
+      <c r="EC168" s="59"/>
+      <c r="ED168" s="59"/>
+      <c r="EE168" s="59"/>
+      <c r="EF168" s="59"/>
+      <c r="EG168" s="59"/>
+      <c r="EH168" s="59"/>
+      <c r="EI168" s="59"/>
+      <c r="EJ168" s="59"/>
+      <c r="EK168" s="59"/>
+      <c r="EL168" s="59"/>
+      <c r="EM168" s="59"/>
+      <c r="EN168" s="59"/>
+      <c r="EO168" s="59"/>
+      <c r="EP168" s="59"/>
+      <c r="EQ168" s="59"/>
+      <c r="ER168" s="59"/>
+      <c r="ES168" s="59"/>
+      <c r="ET168" s="59"/>
+      <c r="EU168" s="59"/>
+      <c r="EV168" s="59"/>
+      <c r="EW168" s="59"/>
+      <c r="EX168" s="59"/>
+      <c r="EY168" s="59"/>
+      <c r="EZ168" s="59"/>
+      <c r="FA168" s="59"/>
+      <c r="FB168" s="59"/>
+      <c r="FC168" s="59"/>
+      <c r="FD168" s="59"/>
+      <c r="FE168" s="59"/>
+      <c r="FF168" s="59"/>
+      <c r="FG168" s="59"/>
+      <c r="FH168" s="59"/>
+      <c r="FI168" s="59"/>
+      <c r="FJ168" s="59"/>
+      <c r="FK168" s="59"/>
+      <c r="FL168" s="59"/>
+      <c r="FM168" s="59"/>
+      <c r="FN168" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="31">
